--- a/Italian Serie A/X_pred.xlsx
+++ b/Italian Serie A/X_pred.xlsx
@@ -1556,13 +1556,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1583,16 +1583,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1604,88 +1604,88 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
         <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1703,25 +1703,25 @@
         <v>1</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
         <v>1</v>
@@ -1736,489 +1736,489 @@
         <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
+        <v>1.974921630094044</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.938244514106583</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>29.07366771159875</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>7.752978056426333</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>131.8006269592476</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>34.8884012539185</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>12.92163009404389</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>51.68652037617555</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1499.555172413793</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>37.47272727272728</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>23.258934169279</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>51.04043887147336</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>99.49655172413794</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>3.876489028213166</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>29.07366771159875</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>67.19247648902822</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>224.1902821316615</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>1141.626018808777</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>842.4902821316615</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>235.4321003134796</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.1902351097178684</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8199081952530229</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.2283145166992717</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.239736615471643</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.1458224961388133</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.6673851674477443</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.354321003134796</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.601890567113138</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>0.121196040401123</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.309415653998025</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>1.385027062752007</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.1845758562008753</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>1</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="FD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
         <v>2.163009404388715</v>
       </c>
-      <c r="BN2" t="n">
-        <v>3.172413793103448</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>36.16551724137931</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>9.517241379310345</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>122.4551724137931</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>41.87586206896552</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9.517241379310345</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>43.14482758620689</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1493.572413793104</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>41.87586206896552</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>20.93793103448276</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>33.62758620689655</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>82.48275862068965</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>3.172413793103448</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>29.82068965517242</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>48.22068965517241</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>181.4620689655173</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>1154.124137931035</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>909.2137931034484</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>250.1131034482759</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0.2109906951286261</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.8187848932676519</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.3610244000806614</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0.7908771929824562</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.1166206199043258</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0.4950975331299978</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.501131034482759</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.621689980920471</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0.1095594526985002</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.226209000557677</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>1.306567977327475</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0.1419574318788413</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>1</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>1</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>1</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>2.170846394984326</v>
-      </c>
       <c r="FF2" t="n">
-        <v>3.523510971786834</v>
+        <v>3.707210031347962</v>
       </c>
       <c r="FG2" t="n">
-        <v>29.59749216300941</v>
+        <v>37.07210031347962</v>
       </c>
       <c r="FH2" t="n">
-        <v>13.38934169278997</v>
+        <v>10.50376175548589</v>
       </c>
       <c r="FI2" t="n">
-        <v>149.3968652037618</v>
+        <v>126.6630094043887</v>
       </c>
       <c r="FJ2" t="n">
-        <v>40.16802507836991</v>
+        <v>40.77931034482759</v>
       </c>
       <c r="FK2" t="n">
-        <v>11.27523510971787</v>
+        <v>11.12163009404389</v>
       </c>
       <c r="FL2" t="n">
-        <v>53.55736677115988</v>
+        <v>40.1614420062696</v>
       </c>
       <c r="FM2" t="n">
-        <v>1627.15736677116</v>
+        <v>1494.623510971787</v>
       </c>
       <c r="FN2" t="n">
-        <v>47.91974921630094</v>
+        <v>44.48652037617555</v>
       </c>
       <c r="FO2" t="n">
-        <v>21.84576802507837</v>
+        <v>19.7717868338558</v>
       </c>
       <c r="FP2" t="n">
-        <v>65.53730407523511</v>
+        <v>38.30783699059561</v>
       </c>
       <c r="FQ2" t="n">
-        <v>80.33605015673982</v>
+        <v>93.91598746081505</v>
       </c>
       <c r="FR2" t="n">
-        <v>1.409404388714734</v>
+        <v>4.94294670846395</v>
       </c>
       <c r="FS2" t="n">
-        <v>28.18808777429467</v>
+        <v>30.2755485893417</v>
       </c>
       <c r="FT2" t="n">
-        <v>64.83260188087775</v>
+        <v>42.63291536050157</v>
       </c>
       <c r="FU2" t="n">
-        <v>270.6056426332289</v>
+        <v>179.1818181818182</v>
       </c>
       <c r="FV2" t="n">
-        <v>1275.510971786834</v>
+        <v>1157.267398119122</v>
       </c>
       <c r="FW2" t="n">
-        <v>918.226959247649</v>
+        <v>907.6485893416929</v>
       </c>
       <c r="FX2" t="n">
-        <v>248.9712852664577</v>
+        <v>242.5751097178684</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.4530228392297357</v>
+        <v>0.2397917599641737</v>
       </c>
       <c r="FZ2" t="n">
-        <v>1.486306413892621</v>
+        <v>0.848833407971339</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.3425279756815808</v>
+        <v>0.254012539184953</v>
       </c>
       <c r="GB2" t="n">
-        <v>1.063215622413115</v>
+        <v>0.7892965148441822</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.1484706045900979</v>
+        <v>0.1061859583610062</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.7755454252504135</v>
+        <v>0.4753261069910319</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.489712852664577</v>
+        <v>2.425751097178683</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.704743722063471</v>
+        <v>1.593023327354689</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.1466773980970333</v>
+        <v>0.1224691030452743</v>
       </c>
       <c r="GH2" t="n">
-        <v>1.496389341854855</v>
+        <v>1.268117536006388</v>
       </c>
       <c r="GI2" t="n">
-        <v>1.521665705948672</v>
+        <v>1.331766711319636</v>
       </c>
       <c r="GJ2" t="n">
-        <v>0.1820729526579827</v>
+        <v>0.1348842334083594</v>
       </c>
       <c r="GK2" t="n">
-        <v>-0.3510971786833856</v>
+        <v>-1.768965517241379</v>
       </c>
       <c r="GL2" t="n">
-        <v>6.568025078369907</v>
+        <v>-7.998432601880875</v>
       </c>
       <c r="GM2" t="n">
-        <v>-3.872100313479624</v>
+        <v>-2.750783699059561</v>
       </c>
       <c r="GN2" t="n">
-        <v>-26.94169278996866</v>
+        <v>5.13761755485892</v>
       </c>
       <c r="GO2" t="n">
-        <v>1.707836990595609</v>
+        <v>-5.890909090909084</v>
       </c>
       <c r="GP2" t="n">
-        <v>-1.757993730407524</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="GQ2" t="n">
-        <v>-10.41253918495298</v>
+        <v>11.52507836990596</v>
       </c>
       <c r="GR2" t="n">
-        <v>-133.5849529780564</v>
+        <v>4.931661442006316</v>
       </c>
       <c r="GS2" t="n">
-        <v>-6.043887147335425</v>
+        <v>-7.013793103448272</v>
       </c>
       <c r="GT2" t="n">
-        <v>-0.9078369905956123</v>
+        <v>3.487147335423199</v>
       </c>
       <c r="GU2" t="n">
-        <v>-31.90971786833856</v>
+        <v>12.73260188087774</v>
       </c>
       <c r="GV2" t="n">
-        <v>2.146708463949835</v>
+        <v>5.580564263322898</v>
       </c>
       <c r="GW2" t="n">
-        <v>1.763009404388715</v>
+        <v>-1.066457680250783</v>
       </c>
       <c r="GX2" t="n">
-        <v>1.632601880877743</v>
+        <v>-1.201880877742948</v>
       </c>
       <c r="GY2" t="n">
-        <v>-16.61191222570533</v>
+        <v>24.55956112852665</v>
       </c>
       <c r="GZ2" t="n">
-        <v>-89.14357366771159</v>
+        <v>45.00846394984328</v>
       </c>
       <c r="HA2" t="n">
-        <v>-121.3868338557995</v>
+        <v>-15.64137931034497</v>
       </c>
       <c r="HB2" t="n">
-        <v>-9.013166144200568</v>
+        <v>-65.15830721003135</v>
       </c>
       <c r="HC2" t="n">
-        <v>1.141818181818223</v>
+        <v>-7.143009404388749</v>
       </c>
       <c r="HD2" t="n">
-        <v>-0.2420321441011096</v>
+        <v>-0.04955665024630537</v>
       </c>
       <c r="HE2" t="n">
-        <v>-0.6675215206249691</v>
+        <v>-0.02892521271831605</v>
       </c>
       <c r="HF2" t="n">
-        <v>0.01849642439908067</v>
+        <v>-0.02569802248568126</v>
       </c>
       <c r="HG2" t="n">
-        <v>-0.2723384294306584</v>
+        <v>0.4504401006274605</v>
       </c>
       <c r="HH2" t="n">
-        <v>-0.0318499846857721</v>
+        <v>0.03963653777780714</v>
       </c>
       <c r="HI2" t="n">
-        <v>-0.2804478921204157</v>
+        <v>0.1920590604567124</v>
       </c>
       <c r="HJ2" t="n">
-        <v>0.01141818181818177</v>
+        <v>-0.07143009404388723</v>
       </c>
       <c r="HK2" t="n">
-        <v>-0.08305374114300013</v>
+        <v>0.008867239758448386</v>
       </c>
       <c r="HL2" t="n">
-        <v>-0.03711794539853304</v>
+        <v>-0.001273062644151293</v>
       </c>
       <c r="HM2" t="n">
-        <v>-0.2701803412971777</v>
+        <v>0.04129811799163696</v>
       </c>
       <c r="HN2" t="n">
-        <v>-0.2150977286211977</v>
+        <v>0.05326035143237129</v>
       </c>
       <c r="HO2" t="n">
-        <v>-0.04011552077914138</v>
+        <v>0.04969162279251585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -2230,16 +2230,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -2248,22 +2248,22 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -2272,7 +2272,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -2290,13 +2290,13 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
@@ -2308,13 +2308,13 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -2338,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -2353,13 +2353,13 @@
         <v>1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -2389,136 +2389,136 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.824451410658307</v>
+        <v>3.315047021943573</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4576802507837</v>
+        <v>2.552978056426333</v>
       </c>
       <c r="BO3" t="n">
-        <v>41.60501567398121</v>
+        <v>38.93291536050157</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.8871473354232</v>
+        <v>7.658934169278997</v>
       </c>
       <c r="BQ3" t="n">
-        <v>139.17868338558</v>
+        <v>169.7730407523511</v>
       </c>
       <c r="BR3" t="n">
-        <v>30.21316614420063</v>
+        <v>45.95360501567399</v>
       </c>
       <c r="BS3" t="n">
-        <v>15.35423197492164</v>
+        <v>20.42382445141066</v>
       </c>
       <c r="BT3" t="n">
-        <v>39.12852664576804</v>
+        <v>65.73918495297806</v>
       </c>
       <c r="BU3" t="n">
-        <v>1514.12539184953</v>
+        <v>1763.469592476489</v>
       </c>
       <c r="BV3" t="n">
-        <v>43.0909090909091</v>
+        <v>44.03887147335424</v>
       </c>
       <c r="BW3" t="n">
-        <v>24.26959247648904</v>
+        <v>21.70031347962383</v>
       </c>
       <c r="BX3" t="n">
-        <v>38.13793103448277</v>
+        <v>42.76238244514107</v>
       </c>
       <c r="BY3" t="n">
-        <v>68.84639498432604</v>
+        <v>53.61253918495299</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.467084639498434</v>
+        <v>6.382445141065832</v>
       </c>
       <c r="CA3" t="n">
-        <v>14.858934169279</v>
+        <v>16.59435736677116</v>
       </c>
       <c r="CB3" t="n">
-        <v>50.5203761755486</v>
+        <v>70.20689655172414</v>
       </c>
       <c r="CC3" t="n">
-        <v>131.7492163009405</v>
+        <v>232.3210031347963</v>
       </c>
       <c r="CD3" t="n">
-        <v>1194.658307210032</v>
+        <v>1463.494670846395</v>
       </c>
       <c r="CE3" t="n">
-        <v>998.0250783699063</v>
+        <v>1146.92539184953</v>
       </c>
       <c r="CF3" t="n">
-        <v>206.3410658307211</v>
+        <v>245.9794357366772</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.2870459425631839</v>
+        <v>0.1675391849529781</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.6825947615602791</v>
+        <v>0.5398484848484848</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1086179398339108</v>
+        <v>0.7932467532467534</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.6157395840698928</v>
+        <v>1.332130857648099</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.0798951645146409</v>
+        <v>0.1477994700651016</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.2788215565839521</v>
+        <v>0.5378832275591737</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.063410658307211</v>
+        <v>2.459794357366771</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.319694106332038</v>
+        <v>1.707119966240656</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1863136845610164</v>
+        <v>0.169201519199535</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.393675252874139</v>
+        <v>1.701581977550199</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.384233256084832</v>
+        <v>1.657568453841366</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1109795102639221</v>
+        <v>0.19562239465631</v>
       </c>
       <c r="CS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX3" t="n">
         <v>1</v>
@@ -2527,19 +2527,19 @@
         <v>1</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>1</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2548,31 +2548,31 @@
         <v>1</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH3" t="n">
         <v>1</v>
       </c>
       <c r="DI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>1</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP3" t="n">
         <v>1</v>
@@ -2590,34 +2590,34 @@
         <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DX3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
         <v>1</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA3" t="n">
         <v>0</v>
       </c>
       <c r="EB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EE3" t="n">
         <v>1</v>
@@ -2629,19 +2629,19 @@
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EI3" t="n">
         <v>1</v>
       </c>
       <c r="EJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK3" t="n">
         <v>1</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM3" t="n">
         <v>1</v>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
@@ -2674,13 +2674,13 @@
         <v>1</v>
       </c>
       <c r="EW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
         <v>1</v>
       </c>
       <c r="EY3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
@@ -2689,202 +2689,202 @@
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>4.663009404388715</v>
+        <v>2.570532915360502</v>
       </c>
       <c r="FF3" t="n">
-        <v>6.624451410658307</v>
+        <v>3.752351097178683</v>
       </c>
       <c r="FG3" t="n">
-        <v>37.53855799373041</v>
+        <v>27.51724137931035</v>
       </c>
       <c r="FH3" t="n">
-        <v>14.90501567398119</v>
+        <v>9.380877742946709</v>
       </c>
       <c r="FI3" t="n">
-        <v>166.1633228840126</v>
+        <v>151.9702194357367</v>
       </c>
       <c r="FJ3" t="n">
-        <v>33.67429467084639</v>
+        <v>50.03134796238244</v>
       </c>
       <c r="FK3" t="n">
-        <v>17.11316614420063</v>
+        <v>13.75862068965517</v>
       </c>
       <c r="FL3" t="n">
-        <v>52.99561128526646</v>
+        <v>45.65360501567397</v>
       </c>
       <c r="FM3" t="n">
-        <v>1931.027586206897</v>
+        <v>1708.57053291536</v>
       </c>
       <c r="FN3" t="n">
-        <v>35.88244514106583</v>
+        <v>62.53918495297805</v>
       </c>
       <c r="FO3" t="n">
-        <v>14.90501567398119</v>
+        <v>24.39028213166144</v>
       </c>
       <c r="FP3" t="n">
-        <v>35.88244514106583</v>
+        <v>45.0282131661442</v>
       </c>
       <c r="FQ3" t="n">
-        <v>54.09968652037618</v>
+        <v>72.54545454545453</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.624451410658307</v>
+        <v>0.6253918495297806</v>
       </c>
       <c r="FS3" t="n">
-        <v>19.87335423197492</v>
+        <v>28.7680250783699</v>
       </c>
       <c r="FT3" t="n">
-        <v>45.26708463949843</v>
+        <v>64.41536050156739</v>
       </c>
       <c r="FU3" t="n">
-        <v>180.5163009404389</v>
+        <v>203.2523510971787</v>
       </c>
       <c r="FV3" t="n">
-        <v>1677.090282131662</v>
+        <v>1321.452978056426</v>
       </c>
       <c r="FW3" t="n">
-        <v>1447.44263322884</v>
+        <v>1001.877742946708</v>
       </c>
       <c r="FX3" t="n">
-        <v>237.6521943573668</v>
+        <v>235.8978056426332</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.4836602308349958</v>
+        <v>0.5315830721003134</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.119758121972072</v>
+        <v>1.156974921630094</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.2230455020423672</v>
+        <v>0.2796223173378345</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.8000117345313732</v>
+        <v>0.8208268025078369</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.08977188455402457</v>
+        <v>0.1050108439045083</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.3004444365689442</v>
+        <v>0.4941927244622644</v>
       </c>
       <c r="GE3" t="n">
-        <v>2.376521943573668</v>
+        <v>2.358978056426333</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.664940984605232</v>
+        <v>1.468264784563197</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1288420547276727</v>
+        <v>0.197624273570015</v>
       </c>
       <c r="GH3" t="n">
-        <v>1.659312682651816</v>
+        <v>1.523268060414352</v>
       </c>
       <c r="GI3" t="n">
-        <v>1.602613486904551</v>
+        <v>1.542156622189107</v>
       </c>
       <c r="GJ3" t="n">
-        <v>0.1186236616566013</v>
+        <v>0.1360632418142729</v>
       </c>
       <c r="GK3" t="n">
-        <v>-2.166771159874607</v>
+        <v>-1.19937304075235</v>
       </c>
       <c r="GL3" t="n">
-        <v>4.066457680250799</v>
+        <v>11.41567398119122</v>
       </c>
       <c r="GM3" t="n">
-        <v>-3.017868338557992</v>
+        <v>-1.721943573667711</v>
       </c>
       <c r="GN3" t="n">
-        <v>-26.98463949843259</v>
+        <v>17.80282131661446</v>
       </c>
       <c r="GO3" t="n">
-        <v>-3.461128526645759</v>
+        <v>-4.077742946708454</v>
       </c>
       <c r="GP3" t="n">
-        <v>-1.758934169278994</v>
+        <v>6.665203761755491</v>
       </c>
       <c r="GQ3" t="n">
-        <v>-13.86708463949842</v>
+        <v>20.08557993730409</v>
       </c>
       <c r="GR3" t="n">
-        <v>-416.9021943573666</v>
+        <v>54.89905956112921</v>
       </c>
       <c r="GS3" t="n">
-        <v>7.208463949843271</v>
+        <v>-18.50031347962381</v>
       </c>
       <c r="GT3" t="n">
-        <v>9.364576802507845</v>
+        <v>-2.689968652037614</v>
       </c>
       <c r="GU3" t="n">
-        <v>2.255485893416939</v>
+        <v>-2.265830721003127</v>
       </c>
       <c r="GV3" t="n">
-        <v>14.74670846394986</v>
+        <v>-18.93291536050155</v>
       </c>
       <c r="GW3" t="n">
-        <v>-3.157366771159873</v>
+        <v>5.757053291536051</v>
       </c>
       <c r="GX3" t="n">
-        <v>-5.014420062695921</v>
+        <v>-12.17366771159874</v>
       </c>
       <c r="GY3" t="n">
-        <v>5.25329153605017</v>
+        <v>5.791536050156751</v>
       </c>
       <c r="GZ3" t="n">
-        <v>-48.76708463949842</v>
+        <v>29.0686520376176</v>
       </c>
       <c r="HA3" t="n">
-        <v>-482.4319749216299</v>
+        <v>142.0416927899691</v>
       </c>
       <c r="HB3" t="n">
-        <v>-449.4175548589338</v>
+        <v>145.0476489028216</v>
       </c>
       <c r="HC3" t="n">
-        <v>-31.31112852664569</v>
+        <v>10.08163009404402</v>
       </c>
       <c r="HD3" t="n">
-        <v>-0.1966142882718118</v>
+        <v>-0.3640438871473353</v>
       </c>
       <c r="HE3" t="n">
-        <v>-0.4371633604117927</v>
+        <v>-0.6171264367816092</v>
       </c>
       <c r="HF3" t="n">
-        <v>-0.1144275622084564</v>
+        <v>0.5136244359089188</v>
       </c>
       <c r="HG3" t="n">
-        <v>-0.1842721504614804</v>
+        <v>0.5113040551402626</v>
       </c>
       <c r="HH3" t="n">
-        <v>-0.009876720039383668</v>
+        <v>0.04278862616059335</v>
       </c>
       <c r="HI3" t="n">
-        <v>-0.02162287998499207</v>
+        <v>0.04369050309690936</v>
       </c>
       <c r="HJ3" t="n">
-        <v>-0.3131112852664573</v>
+        <v>0.1008163009404388</v>
       </c>
       <c r="HK3" t="n">
-        <v>-0.3452468782731941</v>
+        <v>0.2388551816774596</v>
       </c>
       <c r="HL3" t="n">
-        <v>0.05747162983334372</v>
+        <v>-0.02842275437048</v>
       </c>
       <c r="HM3" t="n">
-        <v>-0.2656374297776773</v>
+        <v>0.1783139171358468</v>
       </c>
       <c r="HN3" t="n">
-        <v>-0.2183802308197189</v>
+        <v>0.1154118316522583</v>
       </c>
       <c r="HO3" t="n">
-        <v>-0.007644151392679141</v>
+        <v>0.05955915284203717</v>
       </c>
     </row>
     <row r="4">
@@ -2892,13 +2892,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2919,22 +2919,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -2946,13 +2946,13 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -2961,19 +2961,19 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -2988,19 +2988,19 @@
         <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>1</v>
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -3033,22 +3033,22 @@
         <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
         <v>1</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
         <v>1</v>
@@ -3057,124 +3057,124 @@
         <v>1</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.338557993730408</v>
+        <v>2.053291536050157</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.967398119122258</v>
+        <v>1.941065830721004</v>
       </c>
       <c r="BO4" t="n">
-        <v>33.22695924764891</v>
+        <v>30.08652037617556</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.39811912225705</v>
+        <v>10.19059561128527</v>
       </c>
       <c r="BQ4" t="n">
-        <v>137.8670846394984</v>
+        <v>86.86269592476489</v>
       </c>
       <c r="BR4" t="n">
-        <v>35.21065830721003</v>
+        <v>45.12978056426333</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.918495297805643</v>
+        <v>8.734796238244517</v>
       </c>
       <c r="BT4" t="n">
-        <v>37.19435736677116</v>
+        <v>28.6307210031348</v>
       </c>
       <c r="BU4" t="n">
-        <v>1426.775548589342</v>
+        <v>1067.100940438872</v>
       </c>
       <c r="BV4" t="n">
-        <v>32.23510971786834</v>
+        <v>45.12978056426333</v>
       </c>
       <c r="BW4" t="n">
-        <v>20.82884012539185</v>
+        <v>20.86645768025079</v>
       </c>
       <c r="BX4" t="n">
-        <v>32.23510971786834</v>
+        <v>37.85078369905957</v>
       </c>
       <c r="BY4" t="n">
-        <v>45.62507836990596</v>
+        <v>75.21630094043888</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.951097178683386</v>
+        <v>4.367398119122258</v>
       </c>
       <c r="CA4" t="n">
-        <v>18.34921630094044</v>
+        <v>17.95485893416928</v>
       </c>
       <c r="CB4" t="n">
-        <v>32.23510971786834</v>
+        <v>43.18871473354233</v>
       </c>
       <c r="CC4" t="n">
-        <v>155.2244514106583</v>
+        <v>162.0789968652038</v>
       </c>
       <c r="CD4" t="n">
-        <v>1199.642006269593</v>
+        <v>782.7347962382447</v>
       </c>
       <c r="CE4" t="n">
-        <v>989.3699059561129</v>
+        <v>553.203761755486</v>
       </c>
       <c r="CF4" t="n">
-        <v>202.6844514106583</v>
+        <v>167.8051410658308</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.4624498432601881</v>
+        <v>0.2783542319749217</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.003421107628004</v>
+        <v>0.8269749216300941</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.2944061302681992</v>
+        <v>0.1956821235191142</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.9040787182166493</v>
+        <v>0.7966982860399788</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.07109303160807678</v>
+        <v>0.08414521115544393</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.3336374086441677</v>
+        <v>0.5357467223646806</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.026844514106584</v>
+        <v>1.678051410658308</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.263785563938344</v>
+        <v>1.043111924275002</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.145626261131698</v>
+        <v>0.1155676344341453</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.37937818916583</v>
+        <v>0.8641958852067868</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.34790961057842</v>
+        <v>0.9515638147048769</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.09054652878328773</v>
+        <v>0.1084406384190047</v>
       </c>
       <c r="CS4" t="n">
         <v>1</v>
@@ -3189,16 +3189,16 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
@@ -3213,16 +3213,16 @@
         <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
         <v>1</v>
@@ -3255,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="DS4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="n">
         <v>1</v>
@@ -3264,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
         <v>1</v>
@@ -3291,25 +3291,25 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EL4" t="n">
         <v>1</v>
@@ -3318,28 +3318,28 @@
         <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EP4" t="n">
         <v>1</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
         <v>0</v>
       </c>
       <c r="ET4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV4" t="n">
         <v>1</v>
@@ -3348,225 +3348,225 @@
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY4" t="n">
         <v>0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB4" t="n">
         <v>0</v>
       </c>
       <c r="FC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>4.059561128526646</v>
+        <v>3.824451410658307</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.10282131661442</v>
+        <v>6.541692789968653</v>
       </c>
       <c r="FG4" t="n">
-        <v>35.46081504702195</v>
+        <v>47.97241379310346</v>
       </c>
       <c r="FH4" t="n">
-        <v>12.41128526645768</v>
+        <v>14.17366771159875</v>
       </c>
       <c r="FI4" t="n">
-        <v>144.5028213166144</v>
+        <v>152.6394984326019</v>
       </c>
       <c r="FJ4" t="n">
-        <v>33.24451410658308</v>
+        <v>35.43416927899687</v>
       </c>
       <c r="FK4" t="n">
-        <v>14.62758620689655</v>
+        <v>17.98965517241379</v>
       </c>
       <c r="FL4" t="n">
-        <v>50.97492163009404</v>
+        <v>43.06614420062697</v>
       </c>
       <c r="FM4" t="n">
-        <v>1562.935423197492</v>
+        <v>1672.492789968652</v>
       </c>
       <c r="FN4" t="n">
-        <v>20.83322884012539</v>
+        <v>50.15297805642633</v>
       </c>
       <c r="FO4" t="n">
-        <v>11.96802507836991</v>
+        <v>25.07648902821317</v>
       </c>
       <c r="FP4" t="n">
-        <v>32.8012539184953</v>
+        <v>41.4307210031348</v>
       </c>
       <c r="FQ4" t="n">
-        <v>34.13103448275862</v>
+        <v>80.13573667711599</v>
       </c>
       <c r="FR4" t="n">
-        <v>3.10282131661442</v>
+        <v>3.815987460815047</v>
       </c>
       <c r="FS4" t="n">
-        <v>12.85454545454546</v>
+        <v>15.26394984326019</v>
       </c>
       <c r="FT4" t="n">
-        <v>46.09905956112853</v>
+        <v>53.96896551724139</v>
       </c>
       <c r="FU4" t="n">
-        <v>109.0420062695925</v>
+        <v>143.3721003134796</v>
       </c>
       <c r="FV4" t="n">
-        <v>1372.776802507837</v>
+        <v>1322.512225705329</v>
       </c>
       <c r="FW4" t="n">
-        <v>1179.07210031348</v>
+        <v>1106.091222570533</v>
       </c>
       <c r="FX4" t="n">
-        <v>190.1586206896552</v>
+        <v>227.4873667711599</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.1799043972398204</v>
+        <v>0.4295032668480945</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.7452468743377835</v>
+        <v>0.7967146818698544</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.1108150470219436</v>
+        <v>0.1817136886102403</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.6881086729362591</v>
+        <v>0.6266958998855551</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.08098423832850304</v>
+        <v>0.0874093106687637</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.1797663830823203</v>
+        <v>0.3000354890551948</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.901586206896552</v>
+        <v>2.274873667711599</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.22881574364333</v>
+        <v>1.355152147501286</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.09968756826804476</v>
+        <v>0.2050822011506844</v>
       </c>
       <c r="GH4" t="n">
-        <v>1.448541661974269</v>
+        <v>1.526852164583572</v>
       </c>
       <c r="GI4" t="n">
-        <v>1.377467307503694</v>
+        <v>1.512426206700521</v>
       </c>
       <c r="GJ4" t="n">
-        <v>0.1042079637632331</v>
+        <v>0.1242739890663478</v>
       </c>
       <c r="GK4" t="n">
-        <v>0.8645768025078375</v>
+        <v>-4.600626959247649</v>
       </c>
       <c r="GL4" t="n">
-        <v>-2.233855799373039</v>
+        <v>-17.8858934169279</v>
       </c>
       <c r="GM4" t="n">
-        <v>-0.01316614420062656</v>
+        <v>-3.983072100313478</v>
       </c>
       <c r="GN4" t="n">
-        <v>-6.635736677116</v>
+        <v>-65.776802507837</v>
       </c>
       <c r="GO4" t="n">
-        <v>1.966144200626957</v>
+        <v>9.695611285266466</v>
       </c>
       <c r="GP4" t="n">
-        <v>-4.709090909090909</v>
+        <v>-9.254858934169278</v>
       </c>
       <c r="GQ4" t="n">
-        <v>-13.78056426332288</v>
+        <v>-14.43542319749216</v>
       </c>
       <c r="GR4" t="n">
-        <v>-136.1598746081506</v>
+        <v>-605.3918495297805</v>
       </c>
       <c r="GS4" t="n">
-        <v>11.40188087774295</v>
+        <v>-5.023197492163</v>
       </c>
       <c r="GT4" t="n">
-        <v>8.860815047021946</v>
+        <v>-4.210031347962381</v>
       </c>
       <c r="GU4" t="n">
-        <v>-0.5661442006269581</v>
+        <v>-3.57993730407523</v>
       </c>
       <c r="GV4" t="n">
-        <v>11.49404388714733</v>
+        <v>-4.919435736677102</v>
       </c>
       <c r="GW4" t="n">
-        <v>2.848275862068966</v>
+        <v>0.5514106583072111</v>
       </c>
       <c r="GX4" t="n">
-        <v>5.494670846394985</v>
+        <v>2.690909090909095</v>
       </c>
       <c r="GY4" t="n">
-        <v>-13.86394984326019</v>
+        <v>-10.78025078369906</v>
       </c>
       <c r="GZ4" t="n">
-        <v>46.18244514106584</v>
+        <v>18.70689655172413</v>
       </c>
       <c r="HA4" t="n">
-        <v>-173.1347962382442</v>
+        <v>-539.7774294670845</v>
       </c>
       <c r="HB4" t="n">
-        <v>-189.7021943573668</v>
+        <v>-552.8874608150471</v>
       </c>
       <c r="HC4" t="n">
-        <v>12.52583072100316</v>
+        <v>-59.68222570532916</v>
       </c>
       <c r="HD4" t="n">
-        <v>0.2825454460203677</v>
+        <v>-0.1511490348731729</v>
       </c>
       <c r="HE4" t="n">
-        <v>0.2581742332902207</v>
+        <v>0.03026023976023973</v>
       </c>
       <c r="HF4" t="n">
-        <v>0.1835910832462556</v>
+        <v>0.01396843490887381</v>
       </c>
       <c r="HG4" t="n">
-        <v>0.2159700452803902</v>
+        <v>0.1700023861544238</v>
       </c>
       <c r="HH4" t="n">
-        <v>-0.00989120672042626</v>
+        <v>-0.003264099513319768</v>
       </c>
       <c r="HI4" t="n">
-        <v>0.1538710255618474</v>
+        <v>0.2357112333094858</v>
       </c>
       <c r="HJ4" t="n">
-        <v>0.1252583072100317</v>
+        <v>-0.5968222570532913</v>
       </c>
       <c r="HK4" t="n">
-        <v>0.03496982029501461</v>
+        <v>-0.3120402232262836</v>
       </c>
       <c r="HL4" t="n">
-        <v>0.04593869286365329</v>
+        <v>-0.0895145667165391</v>
       </c>
       <c r="HM4" t="n">
-        <v>-0.06916347280843915</v>
+        <v>-0.6626562793767854</v>
       </c>
       <c r="HN4" t="n">
-        <v>-0.02955769692527332</v>
+        <v>-0.560862391995644</v>
       </c>
       <c r="HO4" t="n">
-        <v>-0.01366143497994537</v>
+        <v>-0.01583335064734306</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -3575,58 +3575,58 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
@@ -3638,28 +3638,28 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>1</v>
@@ -3668,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -3692,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
@@ -3719,16 +3719,16 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -3737,121 +3737,121 @@
         <v>1</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>3.926332288401254</v>
+        <v>2.405956112852665</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.837617554858934</v>
+        <v>3.724137931034483</v>
       </c>
       <c r="BO5" t="n">
-        <v>38.0962382445141</v>
+        <v>34.13793103448276</v>
       </c>
       <c r="BP5" t="n">
-        <v>13.30344827586207</v>
+        <v>9.931034482758621</v>
       </c>
       <c r="BQ5" t="n">
-        <v>162.6648902821316</v>
+        <v>134.6896551724138</v>
       </c>
       <c r="BR5" t="n">
-        <v>37.49153605015673</v>
+        <v>36</v>
       </c>
       <c r="BS5" t="n">
-        <v>12.6987460815047</v>
+        <v>11.17241379310345</v>
       </c>
       <c r="BT5" t="n">
-        <v>50.7949843260188</v>
+        <v>47.17241379310344</v>
       </c>
       <c r="BU5" t="n">
-        <v>1872.762695924764</v>
+        <v>1520.068965517241</v>
       </c>
       <c r="BV5" t="n">
-        <v>38.70094043887147</v>
+        <v>36.62068965517241</v>
       </c>
       <c r="BW5" t="n">
-        <v>22.37398119122257</v>
+        <v>14.89655172413793</v>
       </c>
       <c r="BX5" t="n">
-        <v>39.91034482758619</v>
+        <v>52.13793103448276</v>
       </c>
       <c r="BY5" t="n">
-        <v>60.47021943573667</v>
+        <v>125.3793103448276</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.418808777429467</v>
+        <v>2.482758620689655</v>
       </c>
       <c r="CA5" t="n">
-        <v>24.79278996865203</v>
+        <v>29.79310344827586</v>
       </c>
       <c r="CB5" t="n">
-        <v>48.37617554858933</v>
+        <v>65.79310344827586</v>
       </c>
       <c r="CC5" t="n">
-        <v>221.9257053291536</v>
+        <v>206.6896551724138</v>
       </c>
       <c r="CD5" t="n">
-        <v>1567.992789968652</v>
+        <v>1155.724137931034</v>
       </c>
       <c r="CE5" t="n">
-        <v>1304.34263322884</v>
+        <v>894.4137931034483</v>
       </c>
       <c r="CF5" t="n">
-        <v>249.3187147335423</v>
+        <v>237.1034482758621</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3714599193909538</v>
+        <v>0.3334596438044714</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.071186744290192</v>
+        <v>0.9289503599848428</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.1259796238244514</v>
+        <v>0.2339655172413793</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.8645474392378779</v>
+        <v>0.8808620689655172</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.09768180093187137</v>
+        <v>0.1272705038832485</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.4457069802041087</v>
+        <v>0.5858587613071895</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.493187147335423</v>
+        <v>2.37103448275862</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.361258958872801</v>
+        <v>1.511784142615785</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.1448638485053083</v>
+        <v>0.1113165674711884</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.626891745150731</v>
+        <v>1.346943372708181</v>
       </c>
       <c r="CQ5" t="n">
-        <v>1.609014714562338</v>
+        <v>1.397201653412532</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1232172995464368</v>
+        <v>0.1563457827697879</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU5" t="n">
         <v>1</v>
@@ -3866,7 +3866,7 @@
         <v>1</v>
       </c>
       <c r="CY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ5" t="n">
         <v>0</v>
@@ -3875,19 +3875,19 @@
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD5" t="n">
         <v>1</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG5" t="n">
         <v>1</v>
@@ -3899,28 +3899,28 @@
         <v>1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK5" t="n">
         <v>1</v>
       </c>
       <c r="DL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
         <v>1</v>
@@ -3938,22 +3938,22 @@
         <v>1</v>
       </c>
       <c r="DW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
         <v>1</v>
       </c>
       <c r="DY5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA5" t="n">
         <v>0</v>
       </c>
       <c r="EB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EC5" t="n">
         <v>1</v>
@@ -3965,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG5" t="n">
         <v>1</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
         <v>1</v>
@@ -4016,19 +4016,19 @@
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB5" t="n">
         <v>1</v>
@@ -4037,196 +4037,196 @@
         <v>1</v>
       </c>
       <c r="FD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>2.695924764890282</v>
+        <v>3.53448275862069</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>3.528526645768025</v>
       </c>
       <c r="FG5" t="n">
-        <v>42.33009404388716</v>
+        <v>42.84639498432602</v>
       </c>
       <c r="FH5" t="n">
-        <v>14.11003134796238</v>
+        <v>11.59373040752351</v>
       </c>
       <c r="FI5" t="n">
-        <v>171.548275862069</v>
+        <v>131.5636363636364</v>
       </c>
       <c r="FJ5" t="n">
-        <v>47.52852664576804</v>
+        <v>29.74043887147335</v>
       </c>
       <c r="FK5" t="n">
-        <v>20.05109717868339</v>
+        <v>13.61003134796238</v>
       </c>
       <c r="FL5" t="n">
-        <v>77.97648902821318</v>
+        <v>38.30971786833855</v>
       </c>
       <c r="FM5" t="n">
-        <v>1904.111598746082</v>
+        <v>1590.861442006269</v>
       </c>
       <c r="FN5" t="n">
-        <v>34.9037617554859</v>
+        <v>34.27711598746081</v>
       </c>
       <c r="FO5" t="n">
-        <v>17.08056426332288</v>
+        <v>14.1141065830721</v>
       </c>
       <c r="FP5" t="n">
-        <v>49.01379310344828</v>
+        <v>22.17931034482759</v>
       </c>
       <c r="FQ5" t="n">
-        <v>63.12382445141067</v>
+        <v>51.41567398119122</v>
       </c>
       <c r="FR5" t="n">
-        <v>5.941065830721005</v>
+        <v>3.528526645768025</v>
       </c>
       <c r="FS5" t="n">
-        <v>32.67586206896553</v>
+        <v>8.065203761755486</v>
       </c>
       <c r="FT5" t="n">
-        <v>59.41065830721004</v>
+        <v>39.31786833855799</v>
       </c>
       <c r="FU5" t="n">
-        <v>210.1652037617555</v>
+        <v>125.5147335423197</v>
       </c>
       <c r="FV5" t="n">
-        <v>1581.808777429467</v>
+        <v>1339.32789968652</v>
       </c>
       <c r="FW5" t="n">
-        <v>1275.101253918495</v>
+        <v>1179.03197492163</v>
       </c>
       <c r="FX5" t="n">
-        <v>298.6128213166144</v>
+        <v>220.4825078369905</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>0.2190326914464845</v>
       </c>
       <c r="FZ5" t="n">
-        <v>1.370060915788373</v>
+        <v>0.6991043439319301</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.5010363147823965</v>
+        <v>0.3528526645768024</v>
       </c>
       <c r="GB5" t="n">
-        <v>1.387735567723812</v>
+        <v>0.8917330944917151</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.1861896682861776</v>
+        <v>0.07325716980969665</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.4944804109787807</v>
+        <v>0.2462193107071349</v>
       </c>
       <c r="GE5" t="n">
-        <v>2.986128213166145</v>
+        <v>2.204825078369906</v>
       </c>
       <c r="GF5" t="n">
-        <v>1.950951975621585</v>
+        <v>1.32663436876603</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.110143702618024</v>
+        <v>0.1016976288891968</v>
       </c>
       <c r="GH5" t="n">
-        <v>1.721181461839966</v>
+        <v>1.312256812181858</v>
       </c>
       <c r="GI5" t="n">
-        <v>1.721846765305139</v>
+        <v>1.311892590033751</v>
       </c>
       <c r="GJ5" t="n">
-        <v>0.2357273594220585</v>
+        <v>0.09978767120023029</v>
       </c>
       <c r="GK5" t="n">
-        <v>4.837617554858934</v>
+        <v>0.195611285266458</v>
       </c>
       <c r="GL5" t="n">
-        <v>-4.23385579937306</v>
+        <v>-8.708463949843257</v>
       </c>
       <c r="GM5" t="n">
-        <v>-0.8065830721003167</v>
+        <v>-1.662695924764888</v>
       </c>
       <c r="GN5" t="n">
-        <v>-8.883385579937396</v>
+        <v>3.126018808777417</v>
       </c>
       <c r="GO5" t="n">
-        <v>-10.03699059561131</v>
+        <v>6.259561128526645</v>
       </c>
       <c r="GP5" t="n">
-        <v>-7.352351097178692</v>
+        <v>-2.437617554858933</v>
       </c>
       <c r="GQ5" t="n">
-        <v>-27.18150470219438</v>
+        <v>8.862695924764893</v>
       </c>
       <c r="GR5" t="n">
-        <v>-31.34890282131732</v>
+        <v>-70.7924764890281</v>
       </c>
       <c r="GS5" t="n">
-        <v>3.797178683385567</v>
+        <v>2.343573667711603</v>
       </c>
       <c r="GT5" t="n">
-        <v>5.293416927899681</v>
+        <v>0.782445141065832</v>
       </c>
       <c r="GU5" t="n">
-        <v>-9.103448275862085</v>
+        <v>29.95862068965517</v>
       </c>
       <c r="GV5" t="n">
-        <v>-2.653605015674003</v>
+        <v>73.96363636363637</v>
       </c>
       <c r="GW5" t="n">
-        <v>-3.522257053291538</v>
+        <v>-1.045768025078369</v>
       </c>
       <c r="GX5" t="n">
-        <v>-7.883072100313498</v>
+        <v>21.72789968652037</v>
       </c>
       <c r="GY5" t="n">
-        <v>-11.03448275862071</v>
+        <v>26.47523510971786</v>
       </c>
       <c r="GZ5" t="n">
-        <v>11.76050156739805</v>
+        <v>81.17492163009405</v>
       </c>
       <c r="HA5" t="n">
-        <v>-13.81598746081568</v>
+        <v>-183.6037617554857</v>
       </c>
       <c r="HB5" t="n">
-        <v>29.24137931034443</v>
+        <v>-284.6181818181818</v>
       </c>
       <c r="HC5" t="n">
-        <v>-49.29410658307214</v>
+        <v>16.62094043887154</v>
       </c>
       <c r="HD5" t="n">
-        <v>0.3714599193909538</v>
+        <v>0.1144269523579869</v>
       </c>
       <c r="HE5" t="n">
-        <v>-0.2988741714981809</v>
+        <v>0.2298460160529127</v>
       </c>
       <c r="HF5" t="n">
-        <v>-0.3750566909579451</v>
+        <v>-0.1188871473354231</v>
       </c>
       <c r="HG5" t="n">
-        <v>-0.5231881284859344</v>
+        <v>-0.0108710255261979</v>
       </c>
       <c r="HH5" t="n">
-        <v>-0.08850786735430621</v>
+        <v>0.05401333407355186</v>
       </c>
       <c r="HI5" t="n">
-        <v>-0.048773430774672</v>
+        <v>0.3396394506000546</v>
       </c>
       <c r="HJ5" t="n">
-        <v>-0.4929410658307218</v>
+        <v>0.1662094043887148</v>
       </c>
       <c r="HK5" t="n">
-        <v>-0.5896930167487833</v>
+        <v>0.1851497738497554</v>
       </c>
       <c r="HL5" t="n">
-        <v>0.03472014588728435</v>
+        <v>0.009618938581991601</v>
       </c>
       <c r="HM5" t="n">
-        <v>-0.09428971668923469</v>
+        <v>0.03468656052632357</v>
       </c>
       <c r="HN5" t="n">
-        <v>-0.1128320507428011</v>
+        <v>0.08530906337878186</v>
       </c>
       <c r="HO5" t="n">
-        <v>-0.1125100598756217</v>
+        <v>0.05655811156955763</v>
       </c>
     </row>
     <row r="6">
@@ -4243,19 +4243,19 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -4264,16 +4264,16 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -4291,19 +4291,19 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -4324,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>1</v>
@@ -4354,52 +4354,52 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
         <v>1</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF6" t="n">
         <v>1</v>
@@ -4408,133 +4408,133 @@
         <v>1</v>
       </c>
       <c r="BH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>3.934169278996865</v>
+        <v>3.41692789968652</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.49153605015674</v>
+        <v>3.189968652037618</v>
       </c>
       <c r="BO6" t="n">
-        <v>35.93228840125392</v>
+        <v>40.93793103448276</v>
       </c>
       <c r="BP6" t="n">
-        <v>10.97931034482759</v>
+        <v>10.63322884012539</v>
       </c>
       <c r="BQ6" t="n">
-        <v>137.2413793103448</v>
+        <v>149.3968652037618</v>
       </c>
       <c r="BR6" t="n">
-        <v>29.44451410658307</v>
+        <v>27.64639498432602</v>
       </c>
       <c r="BS6" t="n">
-        <v>12.47648902821317</v>
+        <v>15.94984326018809</v>
       </c>
       <c r="BT6" t="n">
-        <v>46.41253918495298</v>
+        <v>65.92601880877743</v>
       </c>
       <c r="BU6" t="n">
-        <v>1532.112852664577</v>
+        <v>1737.469592476489</v>
       </c>
       <c r="BV6" t="n">
-        <v>35.93228840125392</v>
+        <v>33.49467084639498</v>
       </c>
       <c r="BW6" t="n">
-        <v>18.96426332288401</v>
+        <v>26.05141065830721</v>
       </c>
       <c r="BX6" t="n">
-        <v>46.41253918495298</v>
+        <v>29.7730407523511</v>
       </c>
       <c r="BY6" t="n">
-        <v>79.35047021943575</v>
+        <v>47.317868338558</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.99435736677116</v>
+        <v>2.126645768025079</v>
       </c>
       <c r="CA6" t="n">
-        <v>19.46332288401254</v>
+        <v>12.75987460815047</v>
       </c>
       <c r="CB6" t="n">
-        <v>44.41630094043887</v>
+        <v>47.84952978056427</v>
       </c>
       <c r="CC6" t="n">
-        <v>155.7065830721003</v>
+        <v>150.9918495297806</v>
       </c>
       <c r="CD6" t="n">
-        <v>1246.65078369906</v>
+        <v>1467.917241379311</v>
       </c>
       <c r="CE6" t="n">
-        <v>1010.595611285267</v>
+        <v>1247.277742946708</v>
       </c>
       <c r="CF6" t="n">
-        <v>201.7198746081505</v>
+        <v>224.6269592476489</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.3374219302118989</v>
+        <v>0.1933314334568253</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.7840806528894305</v>
+        <v>0.6621601595896267</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.3329224171857401</v>
+        <v>0.2745362884745825</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.9395354349586326</v>
+        <v>0.8413309134906232</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.08861566480140722</v>
+        <v>0.1143261643570635</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.3160070542035179</v>
+        <v>0.2875238712448884</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.017198746081505</v>
+        <v>2.246269592476489</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.16577287521114</v>
+        <v>1.286107576116796</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.1342222866639432</v>
+        <v>0.1443605078599417</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.366963604155768</v>
+        <v>1.495114385566535</v>
       </c>
       <c r="CQ6" t="n">
-        <v>1.34901341348315</v>
+        <v>1.450597273555479</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.1116272016555899</v>
+        <v>0.1399238134093627</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV6" t="n">
         <v>1</v>
       </c>
       <c r="CW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CY6" t="n">
         <v>1</v>
@@ -4549,19 +4549,19 @@
         <v>0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
         <v>0</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DH6" t="n">
         <v>0</v>
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM6" t="n">
         <v>1</v>
@@ -4585,19 +4585,19 @@
         <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP6" t="n">
         <v>1</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
@@ -4609,16 +4609,16 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA6" t="n">
         <v>1</v>
@@ -4627,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="EC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ED6" t="n">
         <v>1</v>
@@ -4645,46 +4645,46 @@
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EJ6" t="n">
         <v>1</v>
       </c>
       <c r="EK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>1</v>
       </c>
       <c r="EM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER6" t="n">
         <v>1</v>
       </c>
       <c r="ES6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ET6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
@@ -4693,16 +4693,16 @@
         <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC6" t="n">
         <v>1</v>
@@ -4711,419 +4711,865 @@
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.974921630094044</v>
+        <v>3.926332288401254</v>
       </c>
       <c r="FF6" t="n">
-        <v>1.712539184952978</v>
+        <v>3.886206896551724</v>
       </c>
       <c r="FG6" t="n">
-        <v>25.11724137931035</v>
+        <v>41.63793103448276</v>
       </c>
       <c r="FH6" t="n">
-        <v>6.850156739811913</v>
+        <v>13.32413793103448</v>
       </c>
       <c r="FI6" t="n">
-        <v>119.3068965517242</v>
+        <v>165.4413793103448</v>
       </c>
       <c r="FJ6" t="n">
-        <v>35.39247648902822</v>
+        <v>32.7551724137931</v>
       </c>
       <c r="FK6" t="n">
-        <v>13.70031347962383</v>
+        <v>11.65862068965517</v>
       </c>
       <c r="FL6" t="n">
-        <v>47.9510971786834</v>
+        <v>53.85172413793103</v>
       </c>
       <c r="FM6" t="n">
-        <v>1305.525705329154</v>
+        <v>1858.717241379311</v>
       </c>
       <c r="FN6" t="n">
-        <v>29.68401253918496</v>
+        <v>34.97586206896552</v>
       </c>
       <c r="FO6" t="n">
-        <v>17.69623824451411</v>
+        <v>18.87586206896552</v>
       </c>
       <c r="FP6" t="n">
-        <v>54.80125391849531</v>
+        <v>33.86551724137931</v>
       </c>
       <c r="FQ6" t="n">
-        <v>93.04796238244516</v>
+        <v>44.96896551724138</v>
       </c>
       <c r="FR6" t="n">
-        <v>2.85423197492163</v>
+        <v>2.220689655172414</v>
       </c>
       <c r="FS6" t="n">
-        <v>22.83385579937304</v>
+        <v>17.76551724137931</v>
       </c>
       <c r="FT6" t="n">
-        <v>60.50971786833856</v>
+        <v>46.07931034482759</v>
       </c>
       <c r="FU6" t="n">
-        <v>210.071473354232</v>
+        <v>188.7586206896552</v>
       </c>
       <c r="FV6" t="n">
-        <v>988.7059561128527</v>
+        <v>1583.351724137931</v>
       </c>
       <c r="FW6" t="n">
-        <v>711.2746081504703</v>
+        <v>1353.510344827586</v>
       </c>
       <c r="FX6" t="n">
-        <v>203.1071473354232</v>
+        <v>236.9475862068965</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.1724071435356702</v>
+        <v>0.2855172413793103</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.7374050401009651</v>
+        <v>0.9430721003134798</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.1766905508284819</v>
+        <v>0.1156609195402299</v>
       </c>
       <c r="GB6" t="n">
-        <v>1.045297116676427</v>
+        <v>0.9672257053291536</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.1370054943258307</v>
+        <v>0.09052570950722073</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.6322405280052501</v>
+        <v>0.3384910439232046</v>
       </c>
       <c r="GE6" t="n">
-        <v>2.031071473354232</v>
+        <v>2.369475862068966</v>
       </c>
       <c r="GF6" t="n">
-        <v>1.454793388429752</v>
+        <v>1.28574473268212</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.09888649687957962</v>
+        <v>0.1498970625222016</v>
       </c>
       <c r="GH6" t="n">
-        <v>1.186026730581845</v>
+        <v>1.654198181106414</v>
       </c>
       <c r="GI6" t="n">
-        <v>1.245238314206535</v>
+        <v>1.596297240618003</v>
       </c>
       <c r="GJ6" t="n">
-        <v>0.1779667811537128</v>
+        <v>0.1099601585461562</v>
       </c>
       <c r="GK6" t="n">
-        <v>2.778996865203762</v>
+        <v>-0.6962382445141064</v>
       </c>
       <c r="GL6" t="n">
-        <v>10.81504702194357</v>
+        <v>-0.7000000000000028</v>
       </c>
       <c r="GM6" t="n">
-        <v>4.129153605015674</v>
+        <v>-2.690909090909091</v>
       </c>
       <c r="GN6" t="n">
-        <v>17.93448275862067</v>
+        <v>-16.04451410658308</v>
       </c>
       <c r="GO6" t="n">
-        <v>-5.947962382445144</v>
+        <v>-5.108777429467082</v>
       </c>
       <c r="GP6" t="n">
-        <v>-1.22382445141066</v>
+        <v>4.291222570532916</v>
       </c>
       <c r="GQ6" t="n">
-        <v>-1.538557993730414</v>
+        <v>12.0742946708464</v>
       </c>
       <c r="GR6" t="n">
-        <v>226.5871473354232</v>
+        <v>-121.2476489028213</v>
       </c>
       <c r="GS6" t="n">
-        <v>6.248275862068962</v>
+        <v>-1.481191222570537</v>
       </c>
       <c r="GT6" t="n">
-        <v>1.268025078369902</v>
+        <v>7.175548589341695</v>
       </c>
       <c r="GU6" t="n">
-        <v>-8.388714733542322</v>
+        <v>-4.092476489028211</v>
       </c>
       <c r="GV6" t="n">
-        <v>-13.69749216300941</v>
+        <v>2.348902821316621</v>
       </c>
       <c r="GW6" t="n">
-        <v>0.1401253918495295</v>
+        <v>-0.09404388714733525</v>
       </c>
       <c r="GX6" t="n">
-        <v>-3.370532915360503</v>
+        <v>-5.00564263322884</v>
       </c>
       <c r="GY6" t="n">
-        <v>-16.09341692789969</v>
+        <v>1.770219435736678</v>
       </c>
       <c r="GZ6" t="n">
-        <v>-54.36489028213165</v>
+        <v>-37.76677115987462</v>
       </c>
       <c r="HA6" t="n">
-        <v>257.944827586207</v>
+        <v>-115.4344827586206</v>
       </c>
       <c r="HB6" t="n">
-        <v>299.3210031347962</v>
+        <v>-106.2326018808778</v>
       </c>
       <c r="HC6" t="n">
-        <v>-1.387272727272716</v>
+        <v>-12.32062695924765</v>
       </c>
       <c r="HD6" t="n">
-        <v>0.1650147866762287</v>
+        <v>-0.09218580792248504</v>
       </c>
       <c r="HE6" t="n">
-        <v>0.04667561278846544</v>
+        <v>-0.2809119407238531</v>
       </c>
       <c r="HF6" t="n">
-        <v>0.1562318663572582</v>
+        <v>0.1588753689343526</v>
       </c>
       <c r="HG6" t="n">
-        <v>-0.1057616817177945</v>
+        <v>-0.1258947918385305</v>
       </c>
       <c r="HH6" t="n">
-        <v>-0.04838982952442346</v>
+        <v>0.02380045484984278</v>
       </c>
       <c r="HI6" t="n">
-        <v>-0.3162334738017322</v>
+        <v>-0.05096717267831613</v>
       </c>
       <c r="HJ6" t="n">
-        <v>-0.01387272727272748</v>
+        <v>-0.123206269592476</v>
       </c>
       <c r="HK6" t="n">
-        <v>-0.2890205132186121</v>
+        <v>0.0003628434346765186</v>
       </c>
       <c r="HL6" t="n">
-        <v>0.03533578978436355</v>
+        <v>-0.005536554662259885</v>
       </c>
       <c r="HM6" t="n">
-        <v>0.1809368735739221</v>
+        <v>-0.1590837955398792</v>
       </c>
       <c r="HN6" t="n">
-        <v>0.1037750992766151</v>
+        <v>-0.1456999670625241</v>
       </c>
       <c r="HO6" t="n">
-        <v>-0.06633957949812294</v>
+        <v>0.02996365486320646</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
-      <c r="BW7" t="inlineStr"/>
-      <c r="BX7" t="inlineStr"/>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
-      <c r="CA7" t="inlineStr"/>
-      <c r="CB7" t="inlineStr"/>
-      <c r="CC7" t="inlineStr"/>
-      <c r="CD7" t="inlineStr"/>
-      <c r="CE7" t="inlineStr"/>
-      <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="inlineStr"/>
-      <c r="CH7" t="inlineStr"/>
-      <c r="CI7" t="inlineStr"/>
-      <c r="CJ7" t="inlineStr"/>
-      <c r="CK7" t="inlineStr"/>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="inlineStr"/>
-      <c r="CY7" t="inlineStr"/>
-      <c r="CZ7" t="inlineStr"/>
-      <c r="DA7" t="inlineStr"/>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="inlineStr"/>
-      <c r="DD7" t="inlineStr"/>
-      <c r="DE7" t="inlineStr"/>
-      <c r="DF7" t="inlineStr"/>
-      <c r="DG7" t="inlineStr"/>
-      <c r="DH7" t="inlineStr"/>
-      <c r="DI7" t="inlineStr"/>
-      <c r="DJ7" t="inlineStr"/>
-      <c r="DK7" t="inlineStr"/>
-      <c r="DL7" t="inlineStr"/>
-      <c r="DM7" t="inlineStr"/>
-      <c r="DN7" t="inlineStr"/>
-      <c r="DO7" t="inlineStr"/>
-      <c r="DP7" t="inlineStr"/>
-      <c r="DQ7" t="inlineStr"/>
-      <c r="DR7" t="inlineStr"/>
-      <c r="DS7" t="inlineStr"/>
-      <c r="DT7" t="inlineStr"/>
-      <c r="DU7" t="inlineStr"/>
-      <c r="DV7" t="inlineStr"/>
-      <c r="DW7" t="inlineStr"/>
-      <c r="DX7" t="inlineStr"/>
-      <c r="DY7" t="inlineStr"/>
-      <c r="DZ7" t="inlineStr"/>
-      <c r="EA7" t="inlineStr"/>
-      <c r="EB7" t="inlineStr"/>
-      <c r="EC7" t="inlineStr"/>
-      <c r="ED7" t="inlineStr"/>
-      <c r="EE7" t="inlineStr"/>
-      <c r="EF7" t="inlineStr"/>
-      <c r="EG7" t="inlineStr"/>
-      <c r="EH7" t="inlineStr"/>
-      <c r="EI7" t="inlineStr"/>
-      <c r="EJ7" t="inlineStr"/>
-      <c r="EK7" t="inlineStr"/>
-      <c r="EL7" t="inlineStr"/>
-      <c r="EM7" t="inlineStr"/>
-      <c r="EN7" t="inlineStr"/>
-      <c r="EO7" t="inlineStr"/>
-      <c r="EP7" t="inlineStr"/>
-      <c r="EQ7" t="inlineStr"/>
-      <c r="ER7" t="inlineStr"/>
-      <c r="ES7" t="inlineStr"/>
-      <c r="ET7" t="inlineStr"/>
-      <c r="EU7" t="inlineStr"/>
-      <c r="EV7" t="inlineStr"/>
-      <c r="EW7" t="inlineStr"/>
-      <c r="EX7" t="inlineStr"/>
-      <c r="EY7" t="inlineStr"/>
-      <c r="EZ7" t="inlineStr"/>
-      <c r="FA7" t="inlineStr"/>
-      <c r="FB7" t="inlineStr"/>
-      <c r="FC7" t="inlineStr"/>
-      <c r="FD7" t="inlineStr"/>
-      <c r="FE7" t="inlineStr"/>
-      <c r="FF7" t="inlineStr"/>
-      <c r="FG7" t="inlineStr"/>
-      <c r="FH7" t="inlineStr"/>
-      <c r="FI7" t="inlineStr"/>
-      <c r="FJ7" t="inlineStr"/>
-      <c r="FK7" t="inlineStr"/>
-      <c r="FL7" t="inlineStr"/>
-      <c r="FM7" t="inlineStr"/>
-      <c r="FN7" t="inlineStr"/>
-      <c r="FO7" t="inlineStr"/>
-      <c r="FP7" t="inlineStr"/>
-      <c r="FQ7" t="inlineStr"/>
-      <c r="FR7" t="inlineStr"/>
-      <c r="FS7" t="inlineStr"/>
-      <c r="FT7" t="inlineStr"/>
-      <c r="FU7" t="inlineStr"/>
-      <c r="FV7" t="inlineStr"/>
-      <c r="FW7" t="inlineStr"/>
-      <c r="FX7" t="inlineStr"/>
-      <c r="FY7" t="inlineStr"/>
-      <c r="FZ7" t="inlineStr"/>
-      <c r="GA7" t="inlineStr"/>
-      <c r="GB7" t="inlineStr"/>
-      <c r="GC7" t="inlineStr"/>
-      <c r="GD7" t="inlineStr"/>
-      <c r="GE7" t="inlineStr"/>
-      <c r="GF7" t="inlineStr"/>
-      <c r="GG7" t="inlineStr"/>
-      <c r="GH7" t="inlineStr"/>
-      <c r="GI7" t="inlineStr"/>
-      <c r="GJ7" t="inlineStr"/>
-      <c r="GK7" t="inlineStr"/>
-      <c r="GL7" t="inlineStr"/>
-      <c r="GM7" t="inlineStr"/>
-      <c r="GN7" t="inlineStr"/>
-      <c r="GO7" t="inlineStr"/>
-      <c r="GP7" t="inlineStr"/>
-      <c r="GQ7" t="inlineStr"/>
-      <c r="GR7" t="inlineStr"/>
-      <c r="GS7" t="inlineStr"/>
-      <c r="GT7" t="inlineStr"/>
-      <c r="GU7" t="inlineStr"/>
-      <c r="GV7" t="inlineStr"/>
-      <c r="GW7" t="inlineStr"/>
-      <c r="GX7" t="inlineStr"/>
-      <c r="GY7" t="inlineStr"/>
-      <c r="GZ7" t="inlineStr"/>
-      <c r="HA7" t="inlineStr"/>
-      <c r="HB7" t="inlineStr"/>
-      <c r="HC7" t="inlineStr"/>
-      <c r="HD7" t="inlineStr"/>
-      <c r="HE7" t="inlineStr"/>
-      <c r="HF7" t="inlineStr"/>
-      <c r="HG7" t="inlineStr"/>
-      <c r="HH7" t="inlineStr"/>
-      <c r="HI7" t="inlineStr"/>
-      <c r="HJ7" t="inlineStr"/>
-      <c r="HK7" t="inlineStr"/>
-      <c r="HL7" t="inlineStr"/>
-      <c r="HM7" t="inlineStr"/>
-      <c r="HN7" t="inlineStr"/>
-      <c r="HO7" t="inlineStr"/>
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.857366771159875</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4.753918495297806</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>22.18495297805643</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>9.507836990595612</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>114.0940438871474</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>27.46708463949843</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>7.92319749216301</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>36.97492163009404</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1451.001567398119</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>40.14420062695925</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>19.54388714733543</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>35.91849529780564</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>63.38557993730408</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.584639498432602</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>20.07210031347962</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>51.76489028213167</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>1182.141065830721</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>937.5783699059562</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>208.9083072100314</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.6146480478768881</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.220492542984706</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.2861154649947754</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.034017288876223</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.08543013936263352</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.4165419517561296</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.089083072100314</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.344968740191117</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1012138323435033</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.143817180099665</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>1.166152009422513</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.1037750146601551</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>1</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>2.170846394984326</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>2.866457680250784</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>40.13040752351097</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>16.482131661442</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>148.3391849529781</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>42.28025078369907</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>15.04890282131662</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>62.34545454545454</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>1663.97868338558</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>50.87962382445141</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>22.93166144200627</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>55.89592476489028</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>77.39435736677117</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>1.433228840125392</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>24.36489028213166</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>61.62884012539185</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>255.8313479623825</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>1298.505329153605</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>962.4131661442008</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>259.8443887147336</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.2218092252575011</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>1.483328284291773</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.3722051866628669</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>1.188680291495339</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.1697644329470658</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.741600158129517</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>2.598443887147336</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>1.699516125615959</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.14793025613106</v>
+      </c>
+      <c r="GH7" t="n">
+        <v>1.486054295214889</v>
+      </c>
+      <c r="GI7" t="n">
+        <v>1.52771071959031</v>
+      </c>
+      <c r="GJ7" t="n">
+        <v>0.212506735060455</v>
+      </c>
+      <c r="GK7" t="n">
+        <v>1.887460815047022</v>
+      </c>
+      <c r="GL7" t="n">
+        <v>-17.94545454545454</v>
+      </c>
+      <c r="GM7" t="n">
+        <v>-6.974294670846392</v>
+      </c>
+      <c r="GN7" t="n">
+        <v>-34.24514106583071</v>
+      </c>
+      <c r="GO7" t="n">
+        <v>-14.81316614420063</v>
+      </c>
+      <c r="GP7" t="n">
+        <v>-7.125705329153607</v>
+      </c>
+      <c r="GQ7" t="n">
+        <v>-25.3705329153605</v>
+      </c>
+      <c r="GR7" t="n">
+        <v>-212.9771159874608</v>
+      </c>
+      <c r="GS7" t="n">
+        <v>-10.73542319749216</v>
+      </c>
+      <c r="GT7" t="n">
+        <v>-3.387774294670848</v>
+      </c>
+      <c r="GU7" t="n">
+        <v>-19.97742946708464</v>
+      </c>
+      <c r="GV7" t="n">
+        <v>-14.0087774294671</v>
+      </c>
+      <c r="GW7" t="n">
+        <v>0.1514106583072099</v>
+      </c>
+      <c r="GX7" t="n">
+        <v>-4.292789968652038</v>
+      </c>
+      <c r="GY7" t="n">
+        <v>-9.86394984326018</v>
+      </c>
+      <c r="GZ7" t="n">
+        <v>-72.01316614420065</v>
+      </c>
+      <c r="HA7" t="n">
+        <v>-116.364263322884</v>
+      </c>
+      <c r="HB7" t="n">
+        <v>-24.83479623824462</v>
+      </c>
+      <c r="HC7" t="n">
+        <v>-50.93608150470226</v>
+      </c>
+      <c r="HD7" t="n">
+        <v>0.392838822619387</v>
+      </c>
+      <c r="HE7" t="n">
+        <v>-0.2628357413070672</v>
+      </c>
+      <c r="HF7" t="n">
+        <v>-0.08608972166809148</v>
+      </c>
+      <c r="HG7" t="n">
+        <v>-0.1546630026191156</v>
+      </c>
+      <c r="HH7" t="n">
+        <v>-0.08433429358443228</v>
+      </c>
+      <c r="HI7" t="n">
+        <v>-0.3250582063733874</v>
+      </c>
+      <c r="HJ7" t="n">
+        <v>-0.5093608150470219</v>
+      </c>
+      <c r="HK7" t="n">
+        <v>-0.3545473854248422</v>
+      </c>
+      <c r="HL7" t="n">
+        <v>-0.04671642378755661</v>
+      </c>
+      <c r="HM7" t="n">
+        <v>-0.342237115115223</v>
+      </c>
+      <c r="HN7" t="n">
+        <v>-0.3615587101677973</v>
+      </c>
+      <c r="HO7" t="n">
+        <v>-0.1087317204003</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5142,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
@@ -5154,34 +5600,34 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -5199,37 +5645,37 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>1</v>
@@ -5238,22 +5684,22 @@
         <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>1</v>
@@ -5265,19 +5711,19 @@
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -5286,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC8" t="n">
         <v>1</v>
@@ -5304,115 +5750,115 @@
         <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM8" t="n">
-        <v>2.0141065830721</v>
+        <v>2.695924764890282</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.323510971786834</v>
+        <v>0.7131661442006272</v>
       </c>
       <c r="BO8" t="n">
-        <v>23.81598746081504</v>
+        <v>34.2319749216301</v>
       </c>
       <c r="BP8" t="n">
-        <v>7.551410658307209</v>
+        <v>14.26332288401254</v>
       </c>
       <c r="BQ8" t="n">
-        <v>126.6313479623824</v>
+        <v>154.7570532915361</v>
       </c>
       <c r="BR8" t="n">
-        <v>40.08056426332288</v>
+        <v>47.78213166144202</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.61755485893417</v>
+        <v>15.6896551724138</v>
       </c>
       <c r="BT8" t="n">
-        <v>44.14670846394984</v>
+        <v>55.62695924764891</v>
       </c>
       <c r="BU8" t="n">
-        <v>1489.951410658307</v>
+        <v>1738.699059561129</v>
       </c>
       <c r="BV8" t="n">
-        <v>43.56583072100313</v>
+        <v>45.64263322884014</v>
       </c>
       <c r="BW8" t="n">
-        <v>22.65423197492163</v>
+        <v>16.40282131661442</v>
       </c>
       <c r="BX8" t="n">
-        <v>40.08056426332288</v>
+        <v>53.48746081504703</v>
       </c>
       <c r="BY8" t="n">
-        <v>66.22006269592477</v>
+        <v>80.58777429467087</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.742633228840125</v>
+        <v>7.844827586206899</v>
       </c>
       <c r="CA8" t="n">
-        <v>17.42633228840125</v>
+        <v>35.65830721003135</v>
       </c>
       <c r="CB8" t="n">
-        <v>43.56583072100313</v>
+        <v>58.47962382445142</v>
       </c>
       <c r="CC8" t="n">
-        <v>184.1382445141066</v>
+        <v>215.3761755485894</v>
       </c>
       <c r="CD8" t="n">
-        <v>1187.314106583072</v>
+        <v>1399.23197492163</v>
       </c>
       <c r="CE8" t="n">
-        <v>923.0147335423197</v>
+        <v>1108.260188087775</v>
       </c>
       <c r="CF8" t="n">
-        <v>224.3349843260188</v>
+        <v>278.8479623824452</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.2706362211456255</v>
+        <v>0.0891457680250784</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.9052640149818832</v>
+        <v>1.546428232164909</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.5782712402539988</v>
+        <v>0.3514890282131662</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.074251466923881</v>
+        <v>1.105754844685096</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.1104833551882051</v>
+        <v>0.1409383171869455</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.4555576547058748</v>
+        <v>0.577911476487129</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.243349843260188</v>
+        <v>2.788479623824452</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.200614416167329</v>
+        <v>1.874582422975841</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.1237659113568598</v>
+        <v>0.1228738841780522</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.268940618195361</v>
+        <v>1.550395629828253</v>
       </c>
       <c r="CQ8" t="n">
-        <v>1.312675250499272</v>
+        <v>1.588280174393804</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.1393494314112584</v>
+        <v>0.1845399148845075</v>
       </c>
       <c r="CS8" t="n">
         <v>1</v>
@@ -5427,19 +5873,19 @@
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DB8" t="n">
         <v>1</v>
@@ -5448,16 +5894,16 @@
         <v>1</v>
       </c>
       <c r="DD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DE8" t="n">
         <v>1</v>
       </c>
       <c r="DF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
         <v>0</v>
@@ -5466,7 +5912,7 @@
         <v>1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DK8" t="n">
         <v>1</v>
@@ -5475,19 +5921,19 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR8" t="n">
         <v>0</v>
@@ -5508,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="DX8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DY8" t="n">
         <v>1</v>
@@ -5538,52 +5984,52 @@
         <v>0</v>
       </c>
       <c r="EH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP8" t="n">
         <v>1</v>
       </c>
       <c r="EQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ES8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>1</v>
@@ -5592,893 +6038,447 @@
         <v>1</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>3.41692789968652</v>
+        <v>3.934169278996865</v>
       </c>
       <c r="FF8" t="n">
-        <v>4.228526645768025</v>
+        <v>4.631034482758622</v>
       </c>
       <c r="FG8" t="n">
-        <v>50.13824451410659</v>
+        <v>31.57523510971787</v>
       </c>
       <c r="FH8" t="n">
-        <v>13.89373040752351</v>
+        <v>11.36708463949843</v>
       </c>
       <c r="FI8" t="n">
-        <v>169.141065830721</v>
+        <v>115.3548589341693</v>
       </c>
       <c r="FJ8" t="n">
-        <v>33.22413793103448</v>
+        <v>23.99717868338558</v>
       </c>
       <c r="FK8" t="n">
-        <v>15.70595611285267</v>
+        <v>10.52507836990596</v>
       </c>
       <c r="FL8" t="n">
-        <v>83.9664576802508</v>
+        <v>37.46927899686521</v>
       </c>
       <c r="FM8" t="n">
-        <v>1893.775862068966</v>
+        <v>1283.638557993731</v>
       </c>
       <c r="FN8" t="n">
-        <v>39.26489028213167</v>
+        <v>31.99623824451411</v>
       </c>
       <c r="FO8" t="n">
-        <v>29.59968652037618</v>
+        <v>15.57711598746082</v>
       </c>
       <c r="FP8" t="n">
-        <v>34.43228840125392</v>
+        <v>31.57523510971787</v>
       </c>
       <c r="FQ8" t="n">
-        <v>48.32601880877743</v>
+        <v>62.72946708463951</v>
       </c>
       <c r="FR8" t="n">
-        <v>2.416300940438872</v>
+        <v>3.789028213166145</v>
       </c>
       <c r="FS8" t="n">
-        <v>17.51818181818182</v>
+        <v>15.57711598746082</v>
       </c>
       <c r="FT8" t="n">
-        <v>57.99122257053292</v>
+        <v>36.2062695924765</v>
       </c>
       <c r="FU8" t="n">
-        <v>190.8877742946709</v>
+        <v>124.6169278996865</v>
       </c>
       <c r="FV8" t="n">
-        <v>1590.530094043887</v>
+        <v>1044.929780564263</v>
       </c>
       <c r="FW8" t="n">
-        <v>1344.067398119122</v>
+        <v>852.1103448275863</v>
       </c>
       <c r="FX8" t="n">
-        <v>253.7115987460815</v>
+        <v>171.1798746081505</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.2514571552849065</v>
+        <v>0.3206536135590748</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.8037068705918731</v>
+        <v>0.7597713126668746</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.3270307888320593</v>
+        <v>0.2738342900568606</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.925718803277787</v>
+        <v>0.7715353263942608</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.1534229479689475</v>
+        <v>0.07208849649978942</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.377301863292165</v>
+        <v>0.2546549397564594</v>
       </c>
       <c r="GE8" t="n">
-        <v>2.537115987460815</v>
+        <v>1.711798746081505</v>
       </c>
       <c r="GF8" t="n">
-        <v>1.516194998375526</v>
+        <v>0.9697162124582871</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.1727924559212327</v>
+        <v>0.1163728674628544</v>
       </c>
       <c r="GH8" t="n">
-        <v>1.691990915216497</v>
+        <v>1.149364982832431</v>
       </c>
       <c r="GI8" t="n">
-        <v>1.640046007466818</v>
+        <v>1.133808748718295</v>
       </c>
       <c r="GJ8" t="n">
-        <v>0.179429244715012</v>
+        <v>0.09171056183391262</v>
       </c>
       <c r="GK8" t="n">
-        <v>-1.905015673981191</v>
+        <v>-3.917868338557995</v>
       </c>
       <c r="GL8" t="n">
-        <v>-26.32225705329154</v>
+        <v>2.656739811912225</v>
       </c>
       <c r="GM8" t="n">
-        <v>-6.342319749216302</v>
+        <v>2.896238244514107</v>
       </c>
       <c r="GN8" t="n">
-        <v>-42.50971786833857</v>
+        <v>39.40219435736677</v>
       </c>
       <c r="GO8" t="n">
-        <v>6.8564263322884</v>
+        <v>23.78495297805643</v>
       </c>
       <c r="GP8" t="n">
-        <v>-4.088401253918498</v>
+        <v>5.164576802507838</v>
       </c>
       <c r="GQ8" t="n">
-        <v>-39.81974921630096</v>
+        <v>18.1576802507837</v>
       </c>
       <c r="GR8" t="n">
-        <v>-403.8244514106584</v>
+        <v>455.0605015673984</v>
       </c>
       <c r="GS8" t="n">
-        <v>4.300940438871464</v>
+        <v>13.64639498432603</v>
       </c>
       <c r="GT8" t="n">
-        <v>-6.945454545454552</v>
+        <v>0.8257053291536032</v>
       </c>
       <c r="GU8" t="n">
-        <v>5.648275862068964</v>
+        <v>21.91222570532916</v>
       </c>
       <c r="GV8" t="n">
-        <v>17.89404388714733</v>
+        <v>17.85830721003136</v>
       </c>
       <c r="GW8" t="n">
-        <v>-0.6736677115987466</v>
+        <v>4.055799373040754</v>
       </c>
       <c r="GX8" t="n">
-        <v>-0.09184952978056771</v>
+        <v>20.08119122257053</v>
       </c>
       <c r="GY8" t="n">
-        <v>-14.42539184952979</v>
+        <v>22.27335423197492</v>
       </c>
       <c r="GZ8" t="n">
-        <v>-6.749529780564302</v>
+        <v>90.75924764890283</v>
       </c>
       <c r="HA8" t="n">
-        <v>-403.2159874608153</v>
+        <v>354.3021943573669</v>
       </c>
       <c r="HB8" t="n">
-        <v>-421.0526645768026</v>
+        <v>256.1498432601883</v>
       </c>
       <c r="HC8" t="n">
-        <v>-29.37661442006277</v>
+        <v>107.6680877742947</v>
       </c>
       <c r="HD8" t="n">
-        <v>0.01917906586071899</v>
+        <v>-0.2315078455339964</v>
       </c>
       <c r="HE8" t="n">
-        <v>0.1015571443900102</v>
+        <v>0.7866569194980348</v>
       </c>
       <c r="HF8" t="n">
-        <v>0.2512404514219395</v>
+        <v>0.07765473815630564</v>
       </c>
       <c r="HG8" t="n">
-        <v>0.1485326636460935</v>
+        <v>0.334219518290835</v>
       </c>
       <c r="HH8" t="n">
-        <v>-0.04293959278074239</v>
+        <v>0.06884982068715613</v>
       </c>
       <c r="HI8" t="n">
-        <v>0.07825579141370981</v>
+        <v>0.3232565367306696</v>
       </c>
       <c r="HJ8" t="n">
-        <v>-0.2937661442006276</v>
+        <v>1.076680877742947</v>
       </c>
       <c r="HK8" t="n">
-        <v>-0.3155805822081967</v>
+        <v>0.9048662105175534</v>
       </c>
       <c r="HL8" t="n">
-        <v>-0.04902654456437287</v>
+        <v>0.006501016715197788</v>
       </c>
       <c r="HM8" t="n">
-        <v>-0.4230502970211365</v>
+        <v>0.4010306469958211</v>
       </c>
       <c r="HN8" t="n">
-        <v>-0.3273707569675464</v>
+        <v>0.4544714256755087</v>
       </c>
       <c r="HO8" t="n">
-        <v>-0.04007981330375357</v>
+        <v>0.09282935305059488</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>3.53448275862069</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>4.536677115987461</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>40.83009404388715</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>12.60188087774295</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>135.0921630094044</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>23.69153605015674</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>11.59373040752351</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>34.78119122257054</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>1627.15485893417</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>34.78119122257054</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>15.62633228840126</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>25.2037617554859</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>49.39937304075236</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>3.024451410658307</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>10.58557993730408</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>36.79749216300941</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>126.5228840125392</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>1382.678369905956</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>1221.374294670847</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>222.0451410658307</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.3342498880429914</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>0.8431258396775638</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>0.4032601880877744</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1.093363188535602</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>0.06199080309550098</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>0.2354440723738627</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.220451410658307</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.360529082850994</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>0.1067322259281608</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1.346181169165683</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>1.337105057751847</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>0.08233782065392617</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CZ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES9" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EV9" t="n">
-        <v>1</v>
-      </c>
-      <c r="EW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EZ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="FA9" t="n">
-        <v>1</v>
-      </c>
-      <c r="FB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="FC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="FD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="FE9" t="n">
-        <v>3.315047021943573</v>
-      </c>
-      <c r="FF9" t="n">
-        <v>3.191222570532916</v>
-      </c>
-      <c r="FG9" t="n">
-        <v>42.12413793103449</v>
-      </c>
-      <c r="FH9" t="n">
-        <v>10.21191222570533</v>
-      </c>
-      <c r="FI9" t="n">
-        <v>165.305329153605</v>
-      </c>
-      <c r="FJ9" t="n">
-        <v>44.67711598746082</v>
-      </c>
-      <c r="FK9" t="n">
-        <v>20.42382445141066</v>
-      </c>
-      <c r="FL9" t="n">
-        <v>64.4626959247649</v>
-      </c>
-      <c r="FM9" t="n">
-        <v>1738.578056426332</v>
-      </c>
-      <c r="FN9" t="n">
-        <v>44.67711598746082</v>
-      </c>
-      <c r="FO9" t="n">
-        <v>21.70031347962383</v>
-      </c>
-      <c r="FP9" t="n">
-        <v>44.67711598746082</v>
-      </c>
-      <c r="FQ9" t="n">
-        <v>52.9742946708464</v>
-      </c>
-      <c r="FR9" t="n">
-        <v>7.020689655172415</v>
-      </c>
-      <c r="FS9" t="n">
-        <v>14.67962382445141</v>
-      </c>
-      <c r="FT9" t="n">
-        <v>78.50407523510974</v>
-      </c>
-      <c r="FU9" t="n">
-        <v>238.0652037617555</v>
-      </c>
-      <c r="FV9" t="n">
-        <v>1440.517868338558</v>
-      </c>
-      <c r="FW9" t="n">
-        <v>1125.225078369906</v>
-      </c>
-      <c r="FX9" t="n">
-        <v>245.5326645768025</v>
-      </c>
-      <c r="FY9" t="n">
-        <v>0.2313636363636364</v>
-      </c>
-      <c r="FZ9" t="n">
-        <v>0.7951462904911182</v>
-      </c>
-      <c r="GA9" t="n">
-        <v>0.9391312136139723</v>
-      </c>
-      <c r="GB9" t="n">
-        <v>1.514486433107123</v>
-      </c>
-      <c r="GC9" t="n">
-        <v>0.1468520047431758</v>
-      </c>
-      <c r="GD9" t="n">
-        <v>0.5537390815525999</v>
-      </c>
-      <c r="GE9" t="n">
-        <v>2.455326645768025</v>
-      </c>
-      <c r="GF9" t="n">
-        <v>1.664203524774869</v>
-      </c>
-      <c r="GG9" t="n">
-        <v>0.1647961126364666</v>
-      </c>
-      <c r="GH9" t="n">
-        <v>1.658628003160233</v>
-      </c>
-      <c r="GI9" t="n">
-        <v>1.625645204914722</v>
-      </c>
-      <c r="GJ9" t="n">
-        <v>0.1949892957084794</v>
-      </c>
-      <c r="GK9" t="n">
-        <v>1.345454545454546</v>
-      </c>
-      <c r="GL9" t="n">
-        <v>-1.294043887147339</v>
-      </c>
-      <c r="GM9" t="n">
-        <v>2.389968652037616</v>
-      </c>
-      <c r="GN9" t="n">
-        <v>-30.21316614420061</v>
-      </c>
-      <c r="GO9" t="n">
-        <v>-20.98557993730408</v>
-      </c>
-      <c r="GP9" t="n">
-        <v>-8.830094043887152</v>
-      </c>
-      <c r="GQ9" t="n">
-        <v>-29.68150470219436</v>
-      </c>
-      <c r="GR9" t="n">
-        <v>-111.4231974921627</v>
-      </c>
-      <c r="GS9" t="n">
-        <v>-9.895924764890282</v>
-      </c>
-      <c r="GT9" t="n">
-        <v>-6.07398119122257</v>
-      </c>
-      <c r="GU9" t="n">
-        <v>-19.47335423197493</v>
-      </c>
-      <c r="GV9" t="n">
-        <v>-3.574921630094046</v>
-      </c>
-      <c r="GW9" t="n">
-        <v>-3.996238244514108</v>
-      </c>
-      <c r="GX9" t="n">
-        <v>-4.094043887147334</v>
-      </c>
-      <c r="GY9" t="n">
-        <v>-41.70658307210033</v>
-      </c>
-      <c r="GZ9" t="n">
-        <v>-111.5423197492163</v>
-      </c>
-      <c r="HA9" t="n">
-        <v>-57.83949843260189</v>
-      </c>
-      <c r="HB9" t="n">
-        <v>96.14921630094045</v>
-      </c>
-      <c r="HC9" t="n">
-        <v>-23.48752351097181</v>
-      </c>
-      <c r="HD9" t="n">
-        <v>0.1028862516793551</v>
-      </c>
-      <c r="HE9" t="n">
-        <v>0.04797954918644565</v>
-      </c>
-      <c r="HF9" t="n">
-        <v>-0.535871025526198</v>
-      </c>
-      <c r="HG9" t="n">
-        <v>-0.4211232445715207</v>
-      </c>
-      <c r="HH9" t="n">
-        <v>-0.08486120164767483</v>
-      </c>
-      <c r="HI9" t="n">
-        <v>-0.3182950091787372</v>
-      </c>
-      <c r="HJ9" t="n">
-        <v>-0.2348752351097181</v>
-      </c>
-      <c r="HK9" t="n">
-        <v>-0.3036744419238748</v>
-      </c>
-      <c r="HL9" t="n">
-        <v>-0.05806388670830585</v>
-      </c>
-      <c r="HM9" t="n">
-        <v>-0.3124468339945494</v>
-      </c>
-      <c r="HN9" t="n">
-        <v>-0.2885401471628752</v>
-      </c>
-      <c r="HO9" t="n">
-        <v>-0.1126514750545533</v>
-      </c>
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+      <c r="EX9" t="inlineStr"/>
+      <c r="EY9" t="inlineStr"/>
+      <c r="EZ9" t="inlineStr"/>
+      <c r="FA9" t="inlineStr"/>
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="inlineStr"/>
+      <c r="FF9" t="inlineStr"/>
+      <c r="FG9" t="inlineStr"/>
+      <c r="FH9" t="inlineStr"/>
+      <c r="FI9" t="inlineStr"/>
+      <c r="FJ9" t="inlineStr"/>
+      <c r="FK9" t="inlineStr"/>
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="inlineStr"/>
+      <c r="FN9" t="inlineStr"/>
+      <c r="FO9" t="inlineStr"/>
+      <c r="FP9" t="inlineStr"/>
+      <c r="FQ9" t="inlineStr"/>
+      <c r="FR9" t="inlineStr"/>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr"/>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr"/>
+      <c r="FX9" t="inlineStr"/>
+      <c r="FY9" t="inlineStr"/>
+      <c r="FZ9" t="inlineStr"/>
+      <c r="GA9" t="inlineStr"/>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr"/>
+      <c r="GD9" t="inlineStr"/>
+      <c r="GE9" t="inlineStr"/>
+      <c r="GF9" t="inlineStr"/>
+      <c r="GG9" t="inlineStr"/>
+      <c r="GH9" t="inlineStr"/>
+      <c r="GI9" t="inlineStr"/>
+      <c r="GJ9" t="inlineStr"/>
+      <c r="GK9" t="inlineStr"/>
+      <c r="GL9" t="inlineStr"/>
+      <c r="GM9" t="inlineStr"/>
+      <c r="GN9" t="inlineStr"/>
+      <c r="GO9" t="inlineStr"/>
+      <c r="GP9" t="inlineStr"/>
+      <c r="GQ9" t="inlineStr"/>
+      <c r="GR9" t="inlineStr"/>
+      <c r="GS9" t="inlineStr"/>
+      <c r="GT9" t="inlineStr"/>
+      <c r="GU9" t="inlineStr"/>
+      <c r="GV9" t="inlineStr"/>
+      <c r="GW9" t="inlineStr"/>
+      <c r="GX9" t="inlineStr"/>
+      <c r="GY9" t="inlineStr"/>
+      <c r="GZ9" t="inlineStr"/>
+      <c r="HA9" t="inlineStr"/>
+      <c r="HB9" t="inlineStr"/>
+      <c r="HC9" t="inlineStr"/>
+      <c r="HD9" t="inlineStr"/>
+      <c r="HE9" t="inlineStr"/>
+      <c r="HF9" t="inlineStr"/>
+      <c r="HG9" t="inlineStr"/>
+      <c r="HH9" t="inlineStr"/>
+      <c r="HI9" t="inlineStr"/>
+      <c r="HJ9" t="inlineStr"/>
+      <c r="HK9" t="inlineStr"/>
+      <c r="HL9" t="inlineStr"/>
+      <c r="HM9" t="inlineStr"/>
+      <c r="HN9" t="inlineStr"/>
+      <c r="HO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>1</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -6490,7 +6490,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -6499,22 +6499,22 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -6526,13 +6526,13 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -6541,19 +6541,19 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -6568,19 +6568,19 @@
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
         <v>1</v>
@@ -6592,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
@@ -6613,22 +6613,22 @@
         <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" t="n">
         <v>1</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>1</v>
@@ -6637,136 +6637,136 @@
         <v>1</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.053291536050157</v>
+        <v>3.338557993730408</v>
       </c>
       <c r="BN10" t="n">
-        <v>2.449843260188088</v>
+        <v>4.684639498432602</v>
       </c>
       <c r="BO10" t="n">
-        <v>23.51849529780564</v>
+        <v>40.99059561128526</v>
       </c>
       <c r="BP10" t="n">
-        <v>6.859561128526646</v>
+        <v>13.46833855799373</v>
       </c>
       <c r="BQ10" t="n">
-        <v>89.66426332288403</v>
+        <v>155.764263322884</v>
       </c>
       <c r="BR10" t="n">
-        <v>45.07711598746081</v>
+        <v>39.81943573667711</v>
       </c>
       <c r="BS10" t="n">
-        <v>5.389655172413794</v>
+        <v>13.46833855799373</v>
       </c>
       <c r="BT10" t="n">
-        <v>28.90815047021944</v>
+        <v>43.33291536050157</v>
       </c>
       <c r="BU10" t="n">
-        <v>1036.773667711599</v>
+        <v>1622.642006269593</v>
       </c>
       <c r="BV10" t="n">
-        <v>47.5269592476489</v>
+        <v>38.64827586206896</v>
       </c>
       <c r="BW10" t="n">
-        <v>20.57868338557994</v>
+        <v>21.66645768025078</v>
       </c>
       <c r="BX10" t="n">
-        <v>43.60721003134797</v>
+        <v>40.40501567398119</v>
       </c>
       <c r="BY10" t="n">
-        <v>83.29467084639499</v>
+        <v>54.458934169279</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.429780564263323</v>
+        <v>7.026959247648903</v>
       </c>
       <c r="CA10" t="n">
-        <v>21.55862068965518</v>
+        <v>21.08087774294671</v>
       </c>
       <c r="CB10" t="n">
-        <v>45.07711598746081</v>
+        <v>39.23385579937304</v>
       </c>
       <c r="CC10" t="n">
-        <v>171.4890282131662</v>
+        <v>172.7460815047022</v>
       </c>
       <c r="CD10" t="n">
-        <v>747.2021943573668</v>
+        <v>1353.860815047022</v>
       </c>
       <c r="CE10" t="n">
-        <v>508.5874608150471</v>
+        <v>1097.376802507837</v>
       </c>
       <c r="CF10" t="n">
-        <v>164.8744514106583</v>
+        <v>235.8130407523511</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.3627129049111808</v>
+        <v>0.54027454215476</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.7778252351097179</v>
+        <v>1.094289666171699</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.24212087285755</v>
+        <v>0.352634951255641</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.7747231608516876</v>
+        <v>1.12257604464501</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.09081266987408307</v>
+        <v>0.08779274550370962</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.5781555603127425</v>
+        <v>0.388624289961771</v>
       </c>
       <c r="CM10" t="n">
-        <v>1.648744514106583</v>
+        <v>2.358130407523511</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.063176180193756</v>
+        <v>1.486746202673297</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.1302506310096301</v>
+        <v>0.1548108051323789</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.8945683287181281</v>
+        <v>1.55451630787094</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.9774207803265734</v>
+        <v>1.525389586516776</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1086182312417616</v>
+        <v>0.1153524028335369</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>1</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CW10" t="n">
         <v>1</v>
@@ -6775,13 +6775,13 @@
         <v>1</v>
       </c>
       <c r="CY10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CZ10" t="n">
         <v>0</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DB10" t="n">
         <v>1</v>
@@ -6793,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
         <v>1</v>
@@ -6805,28 +6805,28 @@
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM10" t="n">
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
         <v>1</v>
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="DS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
@@ -6853,16 +6853,16 @@
         <v>1</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -6877,16 +6877,16 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK10" t="n">
         <v>1</v>
@@ -6895,28 +6895,28 @@
         <v>1</v>
       </c>
       <c r="EM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER10" t="n">
         <v>1</v>
       </c>
       <c r="ES10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ET10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
         <v>1</v>
@@ -6925,252 +6925,252 @@
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA10" t="n">
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC10" t="n">
         <v>1</v>
       </c>
       <c r="FD10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>1.857366771159875</v>
+        <v>2.586206896551724</v>
       </c>
       <c r="FF10" t="n">
-        <v>5.617554858934168</v>
+        <v>2.563009404388715</v>
       </c>
       <c r="FG10" t="n">
-        <v>27.52601880877743</v>
+        <v>48.0564263322884</v>
       </c>
       <c r="FH10" t="n">
-        <v>10.1115987460815</v>
+        <v>13.45579937304075</v>
       </c>
       <c r="FI10" t="n">
-        <v>112.3510971786834</v>
+        <v>183.2551724137931</v>
       </c>
       <c r="FJ10" t="n">
-        <v>31.45830721003134</v>
+        <v>42.93040752351097</v>
       </c>
       <c r="FK10" t="n">
-        <v>9.549843260188085</v>
+        <v>10.25203761755486</v>
       </c>
       <c r="FL10" t="n">
-        <v>46.06394984326018</v>
+        <v>35.882131661442</v>
       </c>
       <c r="FM10" t="n">
-        <v>1456.63197492163</v>
+        <v>2033.107210031348</v>
       </c>
       <c r="FN10" t="n">
-        <v>45.50219435736676</v>
+        <v>51.2601880877743</v>
       </c>
       <c r="FO10" t="n">
-        <v>24.15548589341692</v>
+        <v>24.34858934169279</v>
       </c>
       <c r="FP10" t="n">
-        <v>34.26708463949843</v>
+        <v>39.0858934169279</v>
       </c>
       <c r="FQ10" t="n">
-        <v>52.24326018808777</v>
+        <v>64.07523510971787</v>
       </c>
       <c r="FR10" t="n">
-        <v>1.685266457680251</v>
+        <v>1.281504702194358</v>
       </c>
       <c r="FS10" t="n">
-        <v>21.90846394984326</v>
+        <v>17.941065830721</v>
       </c>
       <c r="FT10" t="n">
-        <v>48.87272727272726</v>
+        <v>69.2012539184953</v>
       </c>
       <c r="FU10" t="n">
-        <v>190.4351097178683</v>
+        <v>139.0432601880878</v>
       </c>
       <c r="FV10" t="n">
-        <v>1175.192476489028</v>
+        <v>1678.771159874608</v>
       </c>
       <c r="FW10" t="n">
-        <v>925.773040752351</v>
+        <v>1430.159247648903</v>
       </c>
       <c r="FX10" t="n">
-        <v>220.8822570532915</v>
+        <v>272.7042006269593</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.6968910713111339</v>
+        <v>0.1701322875551551</v>
       </c>
       <c r="FZ10" t="n">
-        <v>1.197167722559572</v>
+        <v>0.9074442597128621</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.4521146125501841</v>
+        <v>0.2526603020803648</v>
       </c>
       <c r="GB10" t="n">
-        <v>1.112983656062356</v>
+        <v>0.8968105823121497</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1114670207953203</v>
+        <v>0.06811974046647323</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.4551285659972217</v>
+        <v>0.2695342104011698</v>
       </c>
       <c r="GE10" t="n">
-        <v>2.208822570532915</v>
+        <v>2.727042006269593</v>
       </c>
       <c r="GF10" t="n">
-        <v>1.427229161139008</v>
+        <v>1.651060195702664</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1118127893322126</v>
+        <v>0.2097889814430554</v>
       </c>
       <c r="GH10" t="n">
-        <v>1.121815571959136</v>
+        <v>1.829247358877017</v>
       </c>
       <c r="GI10" t="n">
-        <v>1.1572050625444</v>
+        <v>1.78285947750194</v>
       </c>
       <c r="GJ10" t="n">
-        <v>0.134343758413965</v>
+        <v>0.08678992290614174</v>
       </c>
       <c r="GK10" t="n">
-        <v>-3.16771159874608</v>
+        <v>2.121630094043887</v>
       </c>
       <c r="GL10" t="n">
-        <v>-4.007523510971783</v>
+        <v>-7.065830721003138</v>
       </c>
       <c r="GM10" t="n">
-        <v>-3.252037617554858</v>
+        <v>0.0125391849529759</v>
       </c>
       <c r="GN10" t="n">
-        <v>-22.68683385579935</v>
+        <v>-27.4909090909091</v>
       </c>
       <c r="GO10" t="n">
-        <v>13.61880877742948</v>
+        <v>-3.110971786833858</v>
       </c>
       <c r="GP10" t="n">
-        <v>-4.160188087774292</v>
+        <v>3.216300940438868</v>
       </c>
       <c r="GQ10" t="n">
-        <v>-17.15579937304074</v>
+        <v>7.450783699059564</v>
       </c>
       <c r="GR10" t="n">
-        <v>-419.8583072100312</v>
+        <v>-410.4652037617554</v>
       </c>
       <c r="GS10" t="n">
-        <v>2.024764890282142</v>
+        <v>-12.61191222570533</v>
       </c>
       <c r="GT10" t="n">
-        <v>-3.576802507836984</v>
+        <v>-2.682131661442007</v>
       </c>
       <c r="GU10" t="n">
-        <v>9.34012539184954</v>
+        <v>1.319122257053294</v>
       </c>
       <c r="GV10" t="n">
-        <v>31.05141065830723</v>
+        <v>-9.616300940438869</v>
       </c>
       <c r="GW10" t="n">
-        <v>1.744514106583072</v>
+        <v>5.745454545454545</v>
       </c>
       <c r="GX10" t="n">
-        <v>-0.3498432601880808</v>
+        <v>3.139811912225706</v>
       </c>
       <c r="GY10" t="n">
-        <v>-3.795611285266446</v>
+        <v>-29.96739811912226</v>
       </c>
       <c r="GZ10" t="n">
-        <v>-18.94608150470214</v>
+        <v>33.70282131661443</v>
       </c>
       <c r="HA10" t="n">
-        <v>-427.9902821316612</v>
+        <v>-324.9103448275864</v>
       </c>
       <c r="HB10" t="n">
-        <v>-417.1855799373039</v>
+        <v>-332.7824451410656</v>
       </c>
       <c r="HC10" t="n">
-        <v>-56.0078056426332</v>
+        <v>-36.89115987460821</v>
       </c>
       <c r="HD10" t="n">
-        <v>-0.3341781663999531</v>
+        <v>0.3701422545996049</v>
       </c>
       <c r="HE10" t="n">
-        <v>-0.4193424874498539</v>
+        <v>0.1868454064588368</v>
       </c>
       <c r="HF10" t="n">
-        <v>-0.2099937396926341</v>
+        <v>0.09997464917527621</v>
       </c>
       <c r="HG10" t="n">
-        <v>-0.338260495210668</v>
+        <v>0.2257654623328604</v>
       </c>
       <c r="HH10" t="n">
-        <v>-0.02065435092123719</v>
+        <v>0.01967300503723639</v>
       </c>
       <c r="HI10" t="n">
-        <v>0.1230269943155208</v>
+        <v>0.1190900795606011</v>
       </c>
       <c r="HJ10" t="n">
-        <v>-0.5600780564263323</v>
+        <v>-0.3689115987460818</v>
       </c>
       <c r="HK10" t="n">
-        <v>-0.364052980945252</v>
+        <v>-0.1643139930293673</v>
       </c>
       <c r="HL10" t="n">
-        <v>0.01843784167741747</v>
+        <v>-0.05497817631067653</v>
       </c>
       <c r="HM10" t="n">
-        <v>-0.2272472432410078</v>
+        <v>-0.274731051006077</v>
       </c>
       <c r="HN10" t="n">
-        <v>-0.1797842822178267</v>
+        <v>-0.2574698909851634</v>
       </c>
       <c r="HO10" t="n">
-        <v>-0.02572552717220342</v>
+        <v>0.02856247992739512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -7185,40 +7185,40 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>1</v>
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -7251,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>1</v>
@@ -7275,25 +7275,25 @@
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
         <v>1</v>
@@ -7305,7 +7305,7 @@
         <v>1</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE11" t="n">
         <v>1</v>
@@ -7317,115 +7317,115 @@
         <v>1</v>
       </c>
       <c r="BH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
         <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.586206896551724</v>
+        <v>4.663009404388715</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.746708463949843</v>
+        <v>7.76332288401254</v>
       </c>
       <c r="BO11" t="n">
-        <v>50.58056426332288</v>
+        <v>44.7884012539185</v>
       </c>
       <c r="BP11" t="n">
-        <v>13.73793103448276</v>
+        <v>14.9294670846395</v>
       </c>
       <c r="BQ11" t="n">
-        <v>183.5887147335423</v>
+        <v>180.3479623824452</v>
       </c>
       <c r="BR11" t="n">
-        <v>39.34043887147336</v>
+        <v>38.21943573667712</v>
       </c>
       <c r="BS11" t="n">
-        <v>13.11347962382445</v>
+        <v>22.09561128526646</v>
       </c>
       <c r="BT11" t="n">
-        <v>39.96489028213167</v>
+        <v>70.46708463949845</v>
       </c>
       <c r="BU11" t="n">
-        <v>2025.720376175549</v>
+        <v>2075.793103448276</v>
       </c>
       <c r="BV11" t="n">
-        <v>49.33166144200628</v>
+        <v>36.42789968652038</v>
       </c>
       <c r="BW11" t="n">
-        <v>28.10031347962383</v>
+        <v>14.33228840125392</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.09592476489028</v>
+        <v>44.7884012539185</v>
       </c>
       <c r="BY11" t="n">
-        <v>56.82507836990596</v>
+        <v>47.7742946708464</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.873354231974922</v>
+        <v>6.568965517241381</v>
       </c>
       <c r="CA11" t="n">
-        <v>21.23134796238245</v>
+        <v>16.72100313479624</v>
       </c>
       <c r="CB11" t="n">
-        <v>57.44952978056426</v>
+        <v>53.7460815047022</v>
       </c>
       <c r="CC11" t="n">
-        <v>134.2570532915361</v>
+        <v>185.1253918495298</v>
       </c>
       <c r="CD11" t="n">
-        <v>1700.381191222571</v>
+        <v>1806.46551724138</v>
       </c>
       <c r="CE11" t="n">
-        <v>1460.591849529781</v>
+        <v>1553.858934169279</v>
       </c>
       <c r="CF11" t="n">
-        <v>267.9521003134797</v>
+        <v>256.1896551724138</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.2163669361491503</v>
+        <v>0.5141617982331149</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.8565490166216119</v>
+        <v>1.018295217060891</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.2635784174028689</v>
+        <v>0.440343877647953</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.8739954402963808</v>
+        <v>0.9591051581647193</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.073236361883092</v>
+        <v>0.1209441576173702</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.2491989814908963</v>
+        <v>0.3084243118246636</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.679521003134797</v>
+        <v>2.561896551724138</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.555017642974086</v>
+        <v>1.923440352750698</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.2180657658321437</v>
+        <v>0.1312580089823932</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.829276293663585</v>
+        <v>1.803502196317504</v>
       </c>
       <c r="CQ11" t="n">
-        <v>1.779067197802322</v>
+        <v>1.731703427433435</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.09667025536667172</v>
+        <v>0.158661355207686</v>
       </c>
       <c r="CS11" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
@@ -7443,13 +7443,13 @@
         <v>1</v>
       </c>
       <c r="CX11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>1</v>
       </c>
       <c r="CZ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         <v>1</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DG11" t="n">
         <v>1</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DM11" t="n">
         <v>1</v>
@@ -7506,7 +7506,7 @@
         <v>0</v>
       </c>
       <c r="DS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
@@ -7518,49 +7518,49 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DX11" t="n">
         <v>0</v>
       </c>
       <c r="DY11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DZ11" t="n">
         <v>1</v>
       </c>
       <c r="EA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ED11" t="n">
         <v>1</v>
       </c>
       <c r="EE11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EH11" t="n">
         <v>1</v>
       </c>
       <c r="EI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EL11" t="n">
         <v>1</v>
@@ -7572,13 +7572,13 @@
         <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EP11" t="n">
         <v>1</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
@@ -7593,19 +7593,19 @@
         <v>1</v>
       </c>
       <c r="EV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EX11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EY11" t="n">
         <v>0</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FA11" t="n">
         <v>0</v>
@@ -7614,199 +7614,199 @@
         <v>0</v>
       </c>
       <c r="FC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.570532915360502</v>
+        <v>2.0141065830721</v>
       </c>
       <c r="FF11" t="n">
-        <v>4.790282131661441</v>
+        <v>2.396238244514107</v>
       </c>
       <c r="FG11" t="n">
-        <v>27.37304075235109</v>
+        <v>23.96238244514107</v>
       </c>
       <c r="FH11" t="n">
-        <v>8.896238244514105</v>
+        <v>7.787774294670847</v>
       </c>
       <c r="FI11" t="n">
-        <v>162.1852664576802</v>
+        <v>129.9959247648903</v>
       </c>
       <c r="FJ11" t="n">
-        <v>52.69310344827586</v>
+        <v>44.33040752351098</v>
       </c>
       <c r="FK11" t="n">
-        <v>9.580564263322882</v>
+        <v>9.584952978056426</v>
       </c>
       <c r="FL11" t="n">
-        <v>47.21849529780564</v>
+        <v>35.9435736677116</v>
       </c>
       <c r="FM11" t="n">
-        <v>1821.675862068965</v>
+        <v>1583.913479623824</v>
       </c>
       <c r="FN11" t="n">
-        <v>54.06175548589341</v>
+        <v>49.12288401253918</v>
       </c>
       <c r="FO11" t="n">
-        <v>26.00438871473354</v>
+        <v>26.9576802507837</v>
       </c>
       <c r="FP11" t="n">
-        <v>54.06175548589341</v>
+        <v>38.93887147335423</v>
       </c>
       <c r="FQ11" t="n">
-        <v>86.90940438871472</v>
+        <v>75.48150470219436</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.368652037617555</v>
+        <v>1.79717868338558</v>
       </c>
       <c r="FS11" t="n">
-        <v>34.21630094043887</v>
+        <v>17.37272727272727</v>
       </c>
       <c r="FT11" t="n">
-        <v>67.74827586206897</v>
+        <v>46.12758620689655</v>
       </c>
       <c r="FU11" t="n">
-        <v>222.4059561128526</v>
+        <v>180.3169278996865</v>
       </c>
       <c r="FV11" t="n">
-        <v>1415.186206896552</v>
+        <v>1253.831661442006</v>
       </c>
       <c r="FW11" t="n">
-        <v>1059.336677115987</v>
+        <v>1002.825705329154</v>
       </c>
       <c r="FX11" t="n">
-        <v>254.8430094043887</v>
+        <v>237.9464576802508</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.6957314524555902</v>
+        <v>0.2845532915360502</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.208975966562173</v>
+        <v>0.949937304075235</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.3155436843720542</v>
+        <v>0.4466065830721004</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.998673329022075</v>
+        <v>1.171238244514107</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.1111489985198955</v>
+        <v>0.08820878548873794</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.5516308474275778</v>
+        <v>0.4355042824730838</v>
       </c>
       <c r="GE11" t="n">
-        <v>2.548430094043887</v>
+        <v>2.379464576802508</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.654150221499043</v>
+        <v>1.316940518643165</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.1827390374666675</v>
+        <v>0.1366167743541561</v>
       </c>
       <c r="GH11" t="n">
-        <v>1.625695050438074</v>
+        <v>1.301231923633945</v>
       </c>
       <c r="GI11" t="n">
-        <v>1.653135540345614</v>
+        <v>1.356131891735344</v>
       </c>
       <c r="GJ11" t="n">
-        <v>0.1324549333836786</v>
+        <v>0.1114626975637696</v>
       </c>
       <c r="GK11" t="n">
-        <v>-1.043573667711598</v>
+        <v>5.367084639498433</v>
       </c>
       <c r="GL11" t="n">
-        <v>23.20752351097179</v>
+        <v>20.82601880877743</v>
       </c>
       <c r="GM11" t="n">
-        <v>4.841692789968656</v>
+        <v>7.141692789968655</v>
       </c>
       <c r="GN11" t="n">
-        <v>21.4034482758621</v>
+        <v>50.35203761755488</v>
       </c>
       <c r="GO11" t="n">
-        <v>-13.3526645768025</v>
+        <v>-6.110971786833858</v>
       </c>
       <c r="GP11" t="n">
-        <v>3.532915360501571</v>
+        <v>12.51065830721003</v>
       </c>
       <c r="GQ11" t="n">
-        <v>-7.253605015673969</v>
+        <v>34.52351097178685</v>
       </c>
       <c r="GR11" t="n">
-        <v>204.0445141065834</v>
+        <v>491.879623824452</v>
       </c>
       <c r="GS11" t="n">
-        <v>-4.730094043887135</v>
+        <v>-12.6949843260188</v>
       </c>
       <c r="GT11" t="n">
-        <v>2.095924764890288</v>
+        <v>-12.62539184952978</v>
       </c>
       <c r="GU11" t="n">
-        <v>-20.96583072100313</v>
+        <v>5.849529780564268</v>
       </c>
       <c r="GV11" t="n">
-        <v>-30.08432601880876</v>
+        <v>-27.70721003134796</v>
       </c>
       <c r="GW11" t="n">
-        <v>0.5047021943573669</v>
+        <v>4.771786833855801</v>
       </c>
       <c r="GX11" t="n">
-        <v>-12.98495297805642</v>
+        <v>-0.6517241379310335</v>
       </c>
       <c r="GY11" t="n">
-        <v>-10.2987460815047</v>
+        <v>7.618495297805651</v>
       </c>
       <c r="GZ11" t="n">
-        <v>-88.14890282131657</v>
+        <v>4.808463949843286</v>
       </c>
       <c r="HA11" t="n">
-        <v>285.194984326019</v>
+        <v>552.6338557993731</v>
       </c>
       <c r="HB11" t="n">
-        <v>401.2551724137934</v>
+        <v>551.0332288401254</v>
       </c>
       <c r="HC11" t="n">
-        <v>13.10909090909101</v>
+        <v>18.24319749216301</v>
       </c>
       <c r="HD11" t="n">
-        <v>-0.4793645163064399</v>
+        <v>0.2296085066970647</v>
       </c>
       <c r="HE11" t="n">
-        <v>-0.3524269499405615</v>
+        <v>0.06835791298565619</v>
       </c>
       <c r="HF11" t="n">
-        <v>-0.05196526696918535</v>
+        <v>-0.006262705424147419</v>
       </c>
       <c r="HG11" t="n">
-        <v>-0.1246778887256942</v>
+        <v>-0.2121330863493874</v>
       </c>
       <c r="HH11" t="n">
-        <v>-0.03791263663680347</v>
+        <v>0.03273537212863221</v>
       </c>
       <c r="HI11" t="n">
-        <v>-0.3024318659366816</v>
+        <v>-0.1270799706484202</v>
       </c>
       <c r="HJ11" t="n">
-        <v>0.1310909090909096</v>
+        <v>0.1824319749216303</v>
       </c>
       <c r="HK11" t="n">
-        <v>-0.09913257852495749</v>
+        <v>0.6064998341075334</v>
       </c>
       <c r="HL11" t="n">
-        <v>0.03532672836547621</v>
+        <v>-0.005358765371762914</v>
       </c>
       <c r="HM11" t="n">
-        <v>0.2035812432255111</v>
+        <v>0.5022702726835591</v>
       </c>
       <c r="HN11" t="n">
-        <v>0.1259316574567086</v>
+        <v>0.3755715356980907</v>
       </c>
       <c r="HO11" t="n">
-        <v>-0.03578467801700692</v>
+        <v>0.04719865764391638</v>
       </c>
     </row>
   </sheetData>
